--- a/research/traditional_assets/database/data/turkey/turkey_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_transportation_railroads.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09683459022317523</v>
+        <v>0.09665025374761728</v>
       </c>
       <c r="C2">
-        <v>563.9171542812162</v>
+        <v>560.3161939321092</v>
       </c>
       <c r="D2">
-        <v>560.5771542812162</v>
+        <v>562.6092939321092</v>
       </c>
       <c r="E2">
-        <v>-1.71</v>
+        <v>3.923100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.633100000000001</v>
       </c>
       <c r="G2">
         <v>3.34</v>
@@ -1439,45 +1439,45 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.30137085</v>
       </c>
       <c r="N2">
-        <v>2.751428571428571</v>
+        <v>2.450057721428571</v>
       </c>
       <c r="O2">
-        <v>0.6878571428571428</v>
+        <v>0.6125144303571428</v>
       </c>
       <c r="P2">
-        <v>2.063571428571429</v>
+        <v>1.837543291071428</v>
       </c>
       <c r="Q2">
-        <v>2.383571428571428</v>
+        <v>2.157543291071428</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09683459022317523</v>
+        <v>0.09722121590668412</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4972824581476907</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>9.12971035993883</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09665025374761728</v>
+        <v>0.09653041727205934</v>
       </c>
       <c r="C3">
-        <v>560.3161939321092</v>
+        <v>556.0121016266328</v>
       </c>
       <c r="D3">
-        <v>562.6092939321092</v>
+        <v>563.9383016266328</v>
       </c>
       <c r="E3">
-        <v>3.923100000000001</v>
+        <v>9.5562</v>
       </c>
       <c r="F3">
-        <v>5.633100000000001</v>
+        <v>11.2662</v>
       </c>
       <c r="G3">
         <v>3.34</v>
@@ -1521,45 +1521,45 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M3">
-        <v>0.30137085</v>
+        <v>0.6511863600000001</v>
       </c>
       <c r="N3">
-        <v>2.450057721428571</v>
+        <v>2.100242211428571</v>
       </c>
       <c r="O3">
-        <v>0.6125144303571428</v>
+        <v>0.5250605528571428</v>
       </c>
       <c r="P3">
-        <v>1.837543291071428</v>
+        <v>1.575181658571428</v>
       </c>
       <c r="Q3">
-        <v>2.157543291071428</v>
+        <v>1.895181658571428</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09722121590668412</v>
+        <v>0.09761573191026462</v>
       </c>
       <c r="T3">
-        <v>0.4972824581476907</v>
+        <v>0.5010977294239504</v>
       </c>
       <c r="U3">
-        <v>0.0535</v>
+        <v>0.0578</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.040125</v>
+        <v>0.04335</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y3">
-        <v>9.12971035993883</v>
+        <v>4.22525522713432</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09653041727205934</v>
+        <v>0.09678333079650139</v>
       </c>
       <c r="C4">
-        <v>556.0121016266328</v>
+        <v>547.5814671932402</v>
       </c>
       <c r="D4">
-        <v>563.9383016266328</v>
+        <v>561.1407671932402</v>
       </c>
       <c r="E4">
-        <v>9.5562</v>
+        <v>15.1893</v>
       </c>
       <c r="F4">
-        <v>11.2662</v>
+        <v>16.8993</v>
       </c>
       <c r="G4">
         <v>3.34</v>
@@ -1603,45 +1603,45 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M4">
-        <v>0.6511863600000001</v>
+        <v>1.28096694</v>
       </c>
       <c r="N4">
-        <v>2.100242211428571</v>
+        <v>1.470461631428571</v>
       </c>
       <c r="O4">
-        <v>0.5250605528571428</v>
+        <v>0.3676154078571428</v>
       </c>
       <c r="P4">
-        <v>1.575181658571428</v>
+        <v>1.102846223571428</v>
       </c>
       <c r="Q4">
-        <v>1.895181658571428</v>
+        <v>1.422846223571428</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09761573191026462</v>
+        <v>0.09801838226443443</v>
       </c>
       <c r="T4">
-        <v>0.5010977294239504</v>
+        <v>0.5049916660873495</v>
       </c>
       <c r="U4">
-        <v>0.0578</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04335</v>
+        <v>0.05685</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y4">
-        <v>4.22525522713432</v>
+        <v>2.147930977382266</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09678333079650139</v>
+        <v>0.09922898005332778</v>
       </c>
       <c r="C5">
-        <v>547.5814671932402</v>
+        <v>516.2628029378234</v>
       </c>
       <c r="D5">
-        <v>561.1407671932402</v>
+        <v>535.4552029378234</v>
       </c>
       <c r="E5">
-        <v>15.1893</v>
+        <v>20.8224</v>
       </c>
       <c r="F5">
-        <v>16.8993</v>
+        <v>22.5324</v>
       </c>
       <c r="G5">
         <v>3.34</v>
@@ -1685,45 +1685,45 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M5">
-        <v>1.28096694</v>
+        <v>3.307756320000001</v>
       </c>
       <c r="N5">
-        <v>1.470461631428571</v>
+        <v>-0.5563277485714293</v>
       </c>
       <c r="O5">
-        <v>0.3676154078571428</v>
+        <v>-0.1390819371428573</v>
       </c>
       <c r="P5">
-        <v>1.102846223571428</v>
+        <v>-0.417245811428572</v>
       </c>
       <c r="Q5">
-        <v>1.422846223571428</v>
+        <v>-0.09724581142857214</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09801838226443443</v>
+        <v>0.09851883209788501</v>
       </c>
       <c r="T5">
-        <v>0.5049916660873495</v>
+        <v>0.5098313984618139</v>
       </c>
       <c r="U5">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V5">
-        <v>0.25</v>
+        <v>0.2079527862128437</v>
       </c>
       <c r="W5">
-        <v>0.05685</v>
+        <v>0.1162725309839546</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y5">
-        <v>2.147930977382266</v>
+        <v>0.831811144851375</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09922898005332778</v>
+        <v>0.1048492070059118</v>
       </c>
       <c r="C6">
-        <v>516.2628029378234</v>
+        <v>459.6657710572276</v>
       </c>
       <c r="D6">
-        <v>535.4552029378234</v>
+        <v>484.4912710572276</v>
       </c>
       <c r="E6">
-        <v>20.8224</v>
+        <v>26.4555</v>
       </c>
       <c r="F6">
-        <v>22.5324</v>
+        <v>28.16550000000001</v>
       </c>
       <c r="G6">
         <v>3.34</v>
@@ -1767,45 +1767,45 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M6">
-        <v>3.307756320000001</v>
+        <v>6.641424900000001</v>
       </c>
       <c r="N6">
-        <v>-0.5563277485714293</v>
+        <v>-3.88999632857143</v>
       </c>
       <c r="O6">
-        <v>-0.1390819371428573</v>
+        <v>-0.9724990821428575</v>
       </c>
       <c r="P6">
-        <v>-0.417245811428572</v>
+        <v>-2.917497246428573</v>
       </c>
       <c r="Q6">
-        <v>-0.09724581142857214</v>
+        <v>-2.597497246428573</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09851883209788501</v>
+        <v>0.09924242712268799</v>
       </c>
       <c r="T6">
-        <v>0.5098313984618139</v>
+        <v>0.5168291153825973</v>
       </c>
       <c r="U6">
-        <v>0.1468</v>
+        <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.2079527862128437</v>
+        <v>0.1035707176116894</v>
       </c>
       <c r="W6">
-        <v>0.1162725309839546</v>
+        <v>0.2113780247871636</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y6">
-        <v>0.831811144851375</v>
+        <v>0.4142828704467577</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1048492070059118</v>
+        <v>0.1067492070059118</v>
       </c>
       <c r="C7">
-        <v>459.6657710572276</v>
+        <v>438.9293832503913</v>
       </c>
       <c r="D7">
-        <v>484.4912710572276</v>
+        <v>469.3879832503914</v>
       </c>
       <c r="E7">
-        <v>26.4555</v>
+        <v>32.08860000000001</v>
       </c>
       <c r="F7">
-        <v>28.16550000000001</v>
+        <v>33.79860000000001</v>
       </c>
       <c r="G7">
         <v>3.34</v>
@@ -1849,37 +1849,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M7">
-        <v>6.641424900000001</v>
+        <v>7.969709880000002</v>
       </c>
       <c r="N7">
-        <v>-3.88999632857143</v>
+        <v>-5.218281308571431</v>
       </c>
       <c r="O7">
-        <v>-0.9724990821428575</v>
+        <v>-1.304570327142858</v>
       </c>
       <c r="P7">
-        <v>-2.917497246428573</v>
+        <v>-3.913710981428573</v>
       </c>
       <c r="Q7">
-        <v>-2.597497246428573</v>
+        <v>-3.593710981428573</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09924242712268799</v>
+        <v>0.09981096358143998</v>
       </c>
       <c r="T7">
-        <v>0.5168291153825973</v>
+        <v>0.5223272974611355</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.1035707176116894</v>
+        <v>0.08630893134307452</v>
       </c>
       <c r="W7">
-        <v>0.2113780247871636</v>
+        <v>0.215448353989303</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.4142828704467577</v>
+        <v>0.3452357253722981</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1067492070059118</v>
+        <v>0.1086492070059118</v>
       </c>
       <c r="C8">
-        <v>438.9293832503913</v>
+        <v>419.1061731334592</v>
       </c>
       <c r="D8">
-        <v>469.3879832503914</v>
+        <v>455.1978731334592</v>
       </c>
       <c r="E8">
-        <v>32.0886</v>
+        <v>37.7217</v>
       </c>
       <c r="F8">
-        <v>33.7986</v>
+        <v>39.4317</v>
       </c>
       <c r="G8">
         <v>3.34</v>
@@ -1931,37 +1931,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M8">
-        <v>7.969709880000001</v>
+        <v>9.297994860000001</v>
       </c>
       <c r="N8">
-        <v>-5.218281308571429</v>
+        <v>-6.54656628857143</v>
       </c>
       <c r="O8">
-        <v>-1.304570327142857</v>
+        <v>-1.636641572142858</v>
       </c>
       <c r="P8">
-        <v>-3.913710981428572</v>
+        <v>-4.909924716428573</v>
       </c>
       <c r="Q8">
-        <v>-3.593710981428572</v>
+        <v>-4.589924716428573</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09981096358143998</v>
+        <v>0.1003917266307028</v>
       </c>
       <c r="T8">
-        <v>0.5223272974611355</v>
+        <v>0.5279437200144811</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.08630893134307453</v>
+        <v>0.0739790840083496</v>
       </c>
       <c r="W8">
-        <v>0.215448353989303</v>
+        <v>0.2183557319908312</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.3452357253722982</v>
+        <v>0.2959163360333984</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1086492070059118</v>
+        <v>0.1105492070059118</v>
       </c>
       <c r="C9">
-        <v>419.1061731334592</v>
+        <v>400.1157518789364</v>
       </c>
       <c r="D9">
-        <v>455.1978731334592</v>
+        <v>441.8405518789364</v>
       </c>
       <c r="E9">
-        <v>37.72170000000001</v>
+        <v>43.3548</v>
       </c>
       <c r="F9">
-        <v>39.43170000000001</v>
+        <v>45.06480000000001</v>
       </c>
       <c r="G9">
         <v>3.34</v>
@@ -2013,37 +2013,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M9">
-        <v>9.297994860000001</v>
+        <v>10.62627984</v>
       </c>
       <c r="N9">
-        <v>-6.54656628857143</v>
+        <v>-7.874851268571431</v>
       </c>
       <c r="O9">
-        <v>-1.636641572142858</v>
+        <v>-1.968712817142858</v>
       </c>
       <c r="P9">
-        <v>-4.909924716428573</v>
+        <v>-5.906138451428573</v>
       </c>
       <c r="Q9">
-        <v>-4.589924716428573</v>
+        <v>-5.586138451428573</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1003917266307028</v>
+        <v>0.1009851149636452</v>
       </c>
       <c r="T9">
-        <v>0.5279437200144811</v>
+        <v>0.5336822387102906</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.0739790840083496</v>
+        <v>0.0647316985073059</v>
       </c>
       <c r="W9">
-        <v>0.2183557319908312</v>
+        <v>0.2205362654919773</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.2959163360333984</v>
+        <v>0.2589267940292235</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1105492070059118</v>
+        <v>0.1124492070059118</v>
       </c>
       <c r="C10">
-        <v>400.1157518789364</v>
+        <v>381.8868973863807</v>
       </c>
       <c r="D10">
-        <v>441.8405518789364</v>
+        <v>429.2447973863807</v>
       </c>
       <c r="E10">
-        <v>43.3548</v>
+        <v>48.9879</v>
       </c>
       <c r="F10">
-        <v>45.06480000000001</v>
+        <v>50.6979</v>
       </c>
       <c r="G10">
         <v>3.34</v>
@@ -2095,37 +2095,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M10">
-        <v>10.62627984</v>
+        <v>11.95456482</v>
       </c>
       <c r="N10">
-        <v>-7.874851268571431</v>
+        <v>-9.203136248571431</v>
       </c>
       <c r="O10">
-        <v>-1.968712817142858</v>
+        <v>-2.300784062142858</v>
       </c>
       <c r="P10">
-        <v>-5.906138451428573</v>
+        <v>-6.902352186428573</v>
       </c>
       <c r="Q10">
-        <v>-5.586138451428573</v>
+        <v>-6.582352186428572</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1009851149636452</v>
+        <v>0.1015915447984105</v>
       </c>
       <c r="T10">
-        <v>0.5336822387102906</v>
+        <v>0.5395468786961181</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.0647316985073059</v>
+        <v>0.05753928756204969</v>
       </c>
       <c r="W10">
-        <v>0.2205362654919773</v>
+        <v>0.2222322359928687</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2589267940292235</v>
+        <v>0.2301571502481987</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1124492070059118</v>
+        <v>0.1143492070059118</v>
       </c>
       <c r="C11">
-        <v>381.8868973863807</v>
+        <v>364.3562838970739</v>
       </c>
       <c r="D11">
-        <v>429.2447973863807</v>
+        <v>417.3472838970739</v>
       </c>
       <c r="E11">
-        <v>48.9879</v>
+        <v>54.621</v>
       </c>
       <c r="F11">
-        <v>50.6979</v>
+        <v>56.331</v>
       </c>
       <c r="G11">
         <v>3.34</v>
@@ -2177,37 +2177,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M11">
-        <v>11.95456482</v>
+        <v>13.2828498</v>
       </c>
       <c r="N11">
-        <v>-9.203136248571431</v>
+        <v>-10.53142122857143</v>
       </c>
       <c r="O11">
-        <v>-2.300784062142858</v>
+        <v>-2.632855307142858</v>
       </c>
       <c r="P11">
-        <v>-6.902352186428573</v>
+        <v>-7.898565921428572</v>
       </c>
       <c r="Q11">
-        <v>-6.582352186428572</v>
+        <v>-7.578565921428572</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1015915447984105</v>
+        <v>0.1022114508517262</v>
       </c>
       <c r="T11">
-        <v>0.5395468786961181</v>
+        <v>0.5455418440149639</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.05753928756204969</v>
+        <v>0.05178535880584472</v>
       </c>
       <c r="W11">
-        <v>0.2222322359928687</v>
+        <v>0.2235890123935818</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.2301571502481987</v>
+        <v>0.2071414352233788</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1143492070059118</v>
+        <v>0.1162492070059118</v>
       </c>
       <c r="C12">
-        <v>364.3562838970739</v>
+        <v>347.4674171808085</v>
       </c>
       <c r="D12">
-        <v>417.3472838970739</v>
+        <v>406.0915171808085</v>
       </c>
       <c r="E12">
-        <v>54.62100000000001</v>
+        <v>60.25410000000001</v>
       </c>
       <c r="F12">
-        <v>56.33100000000001</v>
+        <v>61.96410000000001</v>
       </c>
       <c r="G12">
         <v>3.34</v>
@@ -2259,37 +2259,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M12">
-        <v>13.2828498</v>
+        <v>14.61113478</v>
       </c>
       <c r="N12">
-        <v>-10.53142122857143</v>
+        <v>-11.85970620857143</v>
       </c>
       <c r="O12">
-        <v>-2.632855307142858</v>
+        <v>-2.964926552142858</v>
       </c>
       <c r="P12">
-        <v>-7.898565921428574</v>
+        <v>-8.894779656428573</v>
       </c>
       <c r="Q12">
-        <v>-7.578565921428574</v>
+        <v>-8.574779656428573</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1022114508517262</v>
+        <v>0.1028452873781501</v>
       </c>
       <c r="T12">
-        <v>0.5455418440149639</v>
+        <v>0.5516715276555813</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.05178535880584471</v>
+        <v>0.04707759891440429</v>
       </c>
       <c r="W12">
-        <v>0.2235890123935818</v>
+        <v>0.2246991021759835</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.2071414352233788</v>
+        <v>0.1883103956576171</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1162492070059118</v>
+        <v>0.1181492070059117</v>
       </c>
       <c r="C13">
-        <v>347.4674171808085</v>
+        <v>331.1697375043444</v>
       </c>
       <c r="D13">
-        <v>406.0915171808085</v>
+        <v>395.4269375043444</v>
       </c>
       <c r="E13">
-        <v>60.25410000000001</v>
+        <v>65.88720000000001</v>
       </c>
       <c r="F13">
-        <v>61.96410000000001</v>
+        <v>67.5972</v>
       </c>
       <c r="G13">
         <v>3.34</v>
@@ -2341,37 +2341,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M13">
-        <v>14.61113478</v>
+        <v>15.93941976</v>
       </c>
       <c r="N13">
-        <v>-11.85970620857143</v>
+        <v>-13.18799118857143</v>
       </c>
       <c r="O13">
-        <v>-2.964926552142858</v>
+        <v>-3.296997797142858</v>
       </c>
       <c r="P13">
-        <v>-8.894779656428573</v>
+        <v>-9.890993391428573</v>
       </c>
       <c r="Q13">
-        <v>-8.574779656428573</v>
+        <v>-9.570993391428573</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1028452873781501</v>
+        <v>0.1034935292801745</v>
       </c>
       <c r="T13">
-        <v>0.5516715276555813</v>
+        <v>0.557940522288031</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.04707759891440429</v>
+        <v>0.04315446567153727</v>
       </c>
       <c r="W13">
-        <v>0.2246991021759835</v>
+        <v>0.2256241769946515</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1883103956576171</v>
+        <v>0.172617862686149</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1181492070059117</v>
+        <v>0.1200492070059118</v>
       </c>
       <c r="C14">
-        <v>331.1697375043444</v>
+        <v>315.4178603273917</v>
       </c>
       <c r="D14">
-        <v>395.4269375043444</v>
+        <v>385.3081603273917</v>
       </c>
       <c r="E14">
-        <v>65.88720000000001</v>
+        <v>71.52030000000002</v>
       </c>
       <c r="F14">
-        <v>67.5972</v>
+        <v>73.23030000000001</v>
       </c>
       <c r="G14">
         <v>3.34</v>
@@ -2423,37 +2423,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M14">
-        <v>15.93941976</v>
+        <v>17.26770474</v>
       </c>
       <c r="N14">
-        <v>-13.18799118857143</v>
+        <v>-14.51627616857143</v>
       </c>
       <c r="O14">
-        <v>-3.296997797142858</v>
+        <v>-3.629069042142858</v>
       </c>
       <c r="P14">
-        <v>-9.890993391428573</v>
+        <v>-10.88720712642857</v>
       </c>
       <c r="Q14">
-        <v>-9.570993391428573</v>
+        <v>-10.56720712642857</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1034935292801745</v>
+        <v>0.1041566732948892</v>
       </c>
       <c r="T14">
-        <v>0.557940522288031</v>
+        <v>0.5643536317396177</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.04315446567153727</v>
+        <v>0.03983489138911132</v>
       </c>
       <c r="W14">
-        <v>0.2256241769946515</v>
+        <v>0.2264069326104476</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.172617862686149</v>
+        <v>0.1593395655564452</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1200492070059118</v>
+        <v>0.1219492070059117</v>
       </c>
       <c r="C15">
-        <v>315.4178603273917</v>
+        <v>300.1709306710276</v>
       </c>
       <c r="D15">
-        <v>385.3081603273917</v>
+        <v>375.6943306710276</v>
       </c>
       <c r="E15">
-        <v>71.52030000000002</v>
+        <v>77.15340000000002</v>
       </c>
       <c r="F15">
-        <v>73.23030000000001</v>
+        <v>78.86340000000001</v>
       </c>
       <c r="G15">
         <v>3.34</v>
@@ -2505,37 +2505,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M15">
-        <v>17.26770474</v>
+        <v>18.59598972</v>
       </c>
       <c r="N15">
-        <v>-14.51627616857143</v>
+        <v>-15.84456114857143</v>
       </c>
       <c r="O15">
-        <v>-3.629069042142858</v>
+        <v>-3.961140287142858</v>
       </c>
       <c r="P15">
-        <v>-10.88720712642857</v>
+        <v>-11.88342086142857</v>
       </c>
       <c r="Q15">
-        <v>-10.56720712642857</v>
+        <v>-11.56342086142857</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1041566732948892</v>
+        <v>0.1048352392634344</v>
       </c>
       <c r="T15">
-        <v>0.5643536317396177</v>
+        <v>0.5709158832714737</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.03983489138911132</v>
+        <v>0.0369895420041748</v>
       </c>
       <c r="W15">
-        <v>0.2264069326104476</v>
+        <v>0.2270778659954156</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1593395655564452</v>
+        <v>0.1479581680166991</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1219492070059117</v>
+        <v>0.1238492070059118</v>
       </c>
       <c r="C16">
-        <v>300.1709306710276</v>
+        <v>285.3920717881617</v>
       </c>
       <c r="D16">
-        <v>375.6943306710276</v>
+        <v>366.5485717881617</v>
       </c>
       <c r="E16">
-        <v>77.15340000000002</v>
+        <v>82.78650000000003</v>
       </c>
       <c r="F16">
-        <v>78.86340000000001</v>
+        <v>84.49650000000003</v>
       </c>
       <c r="G16">
         <v>3.34</v>
@@ -2587,37 +2587,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M16">
-        <v>18.59598972</v>
+        <v>19.92427470000001</v>
       </c>
       <c r="N16">
-        <v>-15.84456114857143</v>
+        <v>-17.17284612857144</v>
       </c>
       <c r="O16">
-        <v>-3.961140287142858</v>
+        <v>-4.293211532142859</v>
       </c>
       <c r="P16">
-        <v>-11.88342086142857</v>
+        <v>-12.87963459642858</v>
       </c>
       <c r="Q16">
-        <v>-11.56342086142857</v>
+        <v>-12.55963459642858</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1048352392634344</v>
+        <v>0.105529771490063</v>
       </c>
       <c r="T16">
-        <v>0.5709158832714737</v>
+        <v>0.5776325407217263</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.0369895420041748</v>
+        <v>0.0345235725372298</v>
       </c>
       <c r="W16">
-        <v>0.2270778659954156</v>
+        <v>0.2276593415957212</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1479581680166991</v>
+        <v>0.1380942901489193</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1238492070059118</v>
+        <v>0.1257492070059118</v>
       </c>
       <c r="C17">
-        <v>285.3920717881617</v>
+        <v>271.0479124483735</v>
       </c>
       <c r="D17">
-        <v>366.5485717881617</v>
+        <v>357.8375124483735</v>
       </c>
       <c r="E17">
-        <v>82.78650000000002</v>
+        <v>88.41960000000002</v>
       </c>
       <c r="F17">
-        <v>84.49650000000001</v>
+        <v>90.12960000000001</v>
       </c>
       <c r="G17">
         <v>3.34</v>
@@ -2669,37 +2669,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M17">
-        <v>19.92427470000001</v>
+        <v>21.25255968</v>
       </c>
       <c r="N17">
-        <v>-17.17284612857143</v>
+        <v>-18.50113110857143</v>
       </c>
       <c r="O17">
-        <v>-4.293211532142858</v>
+        <v>-4.625282777142858</v>
       </c>
       <c r="P17">
-        <v>-12.87963459642857</v>
+        <v>-13.87584833142857</v>
       </c>
       <c r="Q17">
-        <v>-12.55963459642857</v>
+        <v>-13.55584833142857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.105529771490063</v>
+        <v>0.1062408401982781</v>
       </c>
       <c r="T17">
-        <v>0.5776325407217263</v>
+        <v>0.5845091185874612</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.0345235725372298</v>
+        <v>0.03236584925365295</v>
       </c>
       <c r="W17">
-        <v>0.2276593415957212</v>
+        <v>0.2281681327459887</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1380942901489193</v>
+        <v>0.1294633970146118</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1257492070059118</v>
+        <v>0.1276492070059118</v>
       </c>
       <c r="C18">
-        <v>271.0479124483735</v>
+        <v>257.1081800627621</v>
       </c>
       <c r="D18">
-        <v>357.8375124483735</v>
+        <v>349.5308800627622</v>
       </c>
       <c r="E18">
-        <v>88.41960000000002</v>
+        <v>94.05270000000003</v>
       </c>
       <c r="F18">
-        <v>90.12960000000001</v>
+        <v>95.76270000000002</v>
       </c>
       <c r="G18">
         <v>3.34</v>
@@ -2751,37 +2751,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M18">
-        <v>21.25255968</v>
+        <v>22.58084466000001</v>
       </c>
       <c r="N18">
-        <v>-18.50113110857143</v>
+        <v>-19.82941608857143</v>
       </c>
       <c r="O18">
-        <v>-4.625282777142858</v>
+        <v>-4.957354022142859</v>
       </c>
       <c r="P18">
-        <v>-13.87584833142857</v>
+        <v>-14.87206206642858</v>
       </c>
       <c r="Q18">
-        <v>-13.55584833142857</v>
+        <v>-14.55206206642858</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1062408401982781</v>
+        <v>0.1069690430922332</v>
       </c>
       <c r="T18">
-        <v>0.5845091185874612</v>
+        <v>0.5915513971246595</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.03236584925365295</v>
+        <v>0.03046197576814395</v>
       </c>
       <c r="W18">
-        <v>0.2281681327459887</v>
+        <v>0.2286170661138717</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.1294633970146118</v>
+        <v>0.1218479030725759</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1276492070059118</v>
+        <v>0.1295492070059117</v>
       </c>
       <c r="C19">
-        <v>257.1081800627621</v>
+        <v>243.545349192924</v>
       </c>
       <c r="D19">
-        <v>349.5308800627622</v>
+        <v>341.6011491929241</v>
       </c>
       <c r="E19">
-        <v>94.05270000000003</v>
+        <v>99.68580000000003</v>
       </c>
       <c r="F19">
-        <v>95.76270000000002</v>
+        <v>101.3958</v>
       </c>
       <c r="G19">
         <v>3.34</v>
@@ -2833,37 +2833,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M19">
-        <v>22.58084466000001</v>
+        <v>23.90912964000001</v>
       </c>
       <c r="N19">
-        <v>-19.82941608857143</v>
+        <v>-21.15770106857143</v>
       </c>
       <c r="O19">
-        <v>-4.957354022142859</v>
+        <v>-5.289425267142859</v>
       </c>
       <c r="P19">
-        <v>-14.87206206642858</v>
+        <v>-15.86827580142858</v>
       </c>
       <c r="Q19">
-        <v>-14.55206206642858</v>
+        <v>-15.54827580142858</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1069690430922332</v>
+        <v>0.1077150070323824</v>
       </c>
       <c r="T19">
-        <v>0.5915513971246595</v>
+        <v>0.598765438553009</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.03046197576814395</v>
+        <v>0.02876964378102484</v>
       </c>
       <c r="W19">
-        <v>0.2286170661138717</v>
+        <v>0.2290161179964343</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1218479030725759</v>
+        <v>0.1150785751240994</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1295492070059118</v>
+        <v>0.1314492070059118</v>
       </c>
       <c r="C20">
-        <v>243.545349192924</v>
+        <v>230.3343368437558</v>
       </c>
       <c r="D20">
-        <v>341.601149192924</v>
+        <v>334.0232368437558</v>
       </c>
       <c r="E20">
-        <v>99.68580000000001</v>
+        <v>105.3189</v>
       </c>
       <c r="F20">
-        <v>101.3958</v>
+        <v>107.0289</v>
       </c>
       <c r="G20">
         <v>3.34</v>
@@ -2915,37 +2915,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M20">
-        <v>23.90912964</v>
+        <v>25.23741462</v>
       </c>
       <c r="N20">
-        <v>-21.15770106857143</v>
+        <v>-22.48598604857143</v>
       </c>
       <c r="O20">
-        <v>-5.289425267142858</v>
+        <v>-5.621496512142858</v>
       </c>
       <c r="P20">
-        <v>-15.86827580142857</v>
+        <v>-16.86448953642857</v>
       </c>
       <c r="Q20">
-        <v>-15.54827580142857</v>
+        <v>-16.54448953642857</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1077150070323824</v>
+        <v>0.1084793898352513</v>
       </c>
       <c r="T20">
-        <v>0.598765438553009</v>
+        <v>0.6061576044610709</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.02876964378102484</v>
+        <v>0.02725545200307617</v>
       </c>
       <c r="W20">
-        <v>0.2290161179964343</v>
+        <v>0.2293731644176746</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1150785751240995</v>
+        <v>0.1090218080123048</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1314492070059118</v>
+        <v>0.1333492070059118</v>
       </c>
       <c r="C21">
-        <v>230.3343368437558</v>
+        <v>217.4522374329413</v>
       </c>
       <c r="D21">
-        <v>334.0232368437558</v>
+        <v>326.7742374329413</v>
       </c>
       <c r="E21">
-        <v>105.3189</v>
+        <v>110.952</v>
       </c>
       <c r="F21">
-        <v>107.0289</v>
+        <v>112.662</v>
       </c>
       <c r="G21">
         <v>3.34</v>
@@ -2997,37 +2997,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M21">
-        <v>25.23741462</v>
+        <v>26.56569960000001</v>
       </c>
       <c r="N21">
-        <v>-22.48598604857143</v>
+        <v>-23.81427102857143</v>
       </c>
       <c r="O21">
-        <v>-5.621496512142858</v>
+        <v>-5.953567757142858</v>
       </c>
       <c r="P21">
-        <v>-16.86448953642857</v>
+        <v>-17.86070327142858</v>
       </c>
       <c r="Q21">
-        <v>-16.54448953642857</v>
+        <v>-17.54070327142858</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1084793898352513</v>
+        <v>0.109262882208192</v>
       </c>
       <c r="T21">
-        <v>0.6061576044610709</v>
+        <v>0.6137345745168342</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.02725545200307617</v>
+        <v>0.02589267940292236</v>
       </c>
       <c r="W21">
-        <v>0.2293731644176746</v>
+        <v>0.2296945061967909</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1090218080123048</v>
+        <v>0.1035707176116895</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1333492070059118</v>
+        <v>0.1352492070059118</v>
       </c>
       <c r="C22">
-        <v>217.4522374329413</v>
+        <v>204.878091537682</v>
       </c>
       <c r="D22">
-        <v>326.7742374329413</v>
+        <v>319.833191537682</v>
       </c>
       <c r="E22">
-        <v>110.952</v>
+        <v>116.5851</v>
       </c>
       <c r="F22">
-        <v>112.662</v>
+        <v>118.2951</v>
       </c>
       <c r="G22">
         <v>3.34</v>
@@ -3079,37 +3079,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M22">
-        <v>26.56569960000001</v>
+        <v>27.89398458000001</v>
       </c>
       <c r="N22">
-        <v>-23.81427102857143</v>
+        <v>-25.14255600857143</v>
       </c>
       <c r="O22">
-        <v>-5.953567757142858</v>
+        <v>-6.285639002142858</v>
       </c>
       <c r="P22">
-        <v>-17.86070327142858</v>
+        <v>-18.85691700642857</v>
       </c>
       <c r="Q22">
-        <v>-17.54070327142858</v>
+        <v>-18.53691700642857</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.109262882208192</v>
+        <v>0.1100662098310805</v>
       </c>
       <c r="T22">
-        <v>0.6137345745168342</v>
+        <v>0.6215033665993259</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.02589267940292236</v>
+        <v>0.02465969466944986</v>
       </c>
       <c r="W22">
-        <v>0.2296945061967909</v>
+        <v>0.2299852439969437</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1035707176116895</v>
+        <v>0.09863877867779947</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1352492070059118</v>
+        <v>0.1371492070059118</v>
       </c>
       <c r="C23">
-        <v>204.878091537682</v>
+        <v>192.5926835008725</v>
       </c>
       <c r="D23">
-        <v>319.833191537682</v>
+        <v>313.1808835008725</v>
       </c>
       <c r="E23">
-        <v>116.5851</v>
+        <v>122.2182</v>
       </c>
       <c r="F23">
-        <v>118.2951</v>
+        <v>123.9282</v>
       </c>
       <c r="G23">
         <v>3.34</v>
@@ -3161,37 +3161,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M23">
-        <v>27.89398458</v>
+        <v>29.22226956</v>
       </c>
       <c r="N23">
-        <v>-25.14255600857143</v>
+        <v>-26.47084098857143</v>
       </c>
       <c r="O23">
-        <v>-6.285639002142857</v>
+        <v>-6.617710247142858</v>
       </c>
       <c r="P23">
-        <v>-18.85691700642857</v>
+        <v>-19.85313074142857</v>
       </c>
       <c r="Q23">
-        <v>-18.53691700642857</v>
+        <v>-19.53313074142857</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1100662098310805</v>
+        <v>0.1108901355981456</v>
       </c>
       <c r="T23">
-        <v>0.6215033665993258</v>
+        <v>0.6294713584788043</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.02465969466944987</v>
+        <v>0.02353879945720214</v>
       </c>
       <c r="W23">
-        <v>0.2299852439969437</v>
+        <v>0.2302495510879917</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.09863877867779947</v>
+        <v>0.09415519782880866</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1371492070059118</v>
+        <v>0.1390492070059118</v>
       </c>
       <c r="C24">
-        <v>192.5926835008725</v>
+        <v>180.5783637805382</v>
       </c>
       <c r="D24">
-        <v>313.1808835008725</v>
+        <v>306.7996637805383</v>
       </c>
       <c r="E24">
-        <v>122.2182</v>
+        <v>127.8513</v>
       </c>
       <c r="F24">
-        <v>123.9282</v>
+        <v>129.5613</v>
       </c>
       <c r="G24">
         <v>3.34</v>
@@ -3243,37 +3243,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M24">
-        <v>29.22226956</v>
+        <v>30.55055454</v>
       </c>
       <c r="N24">
-        <v>-26.47084098857143</v>
+        <v>-27.79912596857143</v>
       </c>
       <c r="O24">
-        <v>-6.617710247142858</v>
+        <v>-6.949781492142858</v>
       </c>
       <c r="P24">
-        <v>-19.85313074142857</v>
+        <v>-20.84934447642857</v>
       </c>
       <c r="Q24">
-        <v>-19.53313074142857</v>
+        <v>-20.52934447642857</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1108901355981456</v>
+        <v>0.1117354620344852</v>
       </c>
       <c r="T24">
-        <v>0.6294713584788043</v>
+        <v>0.6376463111863213</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.02353879945720214</v>
+        <v>0.02251537339384553</v>
       </c>
       <c r="W24">
-        <v>0.2302495510879917</v>
+        <v>0.2304908749537312</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.09415519782880866</v>
+        <v>0.09006149357538218</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1390492070059118</v>
+        <v>0.1409492070059118</v>
       </c>
       <c r="C25">
-        <v>180.5783637805382</v>
+        <v>168.81889258391</v>
       </c>
       <c r="D25">
-        <v>306.7996637805383</v>
+        <v>300.67329258391</v>
       </c>
       <c r="E25">
-        <v>127.8513</v>
+        <v>133.4844</v>
       </c>
       <c r="F25">
-        <v>129.5613</v>
+        <v>135.1944</v>
       </c>
       <c r="G25">
         <v>3.34</v>
@@ -3325,37 +3325,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M25">
-        <v>30.55055454</v>
+        <v>31.87883952000001</v>
       </c>
       <c r="N25">
-        <v>-27.79912596857143</v>
+        <v>-29.12741094857143</v>
       </c>
       <c r="O25">
-        <v>-6.949781492142858</v>
+        <v>-7.281852737142859</v>
       </c>
       <c r="P25">
-        <v>-20.84934447642857</v>
+        <v>-21.84555821142857</v>
       </c>
       <c r="Q25">
-        <v>-20.52934447642857</v>
+        <v>-21.52555821142857</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1117354620344852</v>
+        <v>0.11260303390336</v>
       </c>
       <c r="T25">
-        <v>0.6376463111863213</v>
+        <v>0.6460363942282467</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.02251537339384553</v>
+        <v>0.02157723283576863</v>
       </c>
       <c r="W25">
-        <v>0.2304908749537312</v>
+        <v>0.2307120884973258</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.09006149357538218</v>
+        <v>0.0863089313430746</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1409492070059118</v>
+        <v>0.1428492070059117</v>
       </c>
       <c r="C26">
-        <v>168.8188925839101</v>
+        <v>157.2993018692088</v>
       </c>
       <c r="D26">
-        <v>300.6732925839101</v>
+        <v>294.7868018692088</v>
       </c>
       <c r="E26">
-        <v>133.4844</v>
+        <v>139.1175</v>
       </c>
       <c r="F26">
-        <v>135.1944</v>
+        <v>140.8275</v>
       </c>
       <c r="G26">
         <v>3.34</v>
@@ -3407,37 +3407,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M26">
-        <v>31.87883952</v>
+        <v>33.20712450000001</v>
       </c>
       <c r="N26">
-        <v>-29.12741094857143</v>
+        <v>-30.45569592857143</v>
       </c>
       <c r="O26">
-        <v>-7.281852737142858</v>
+        <v>-7.613923982142858</v>
       </c>
       <c r="P26">
-        <v>-21.84555821142857</v>
+        <v>-22.84177194642858</v>
       </c>
       <c r="Q26">
-        <v>-21.52555821142857</v>
+        <v>-22.52177194642858</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.11260303390336</v>
+        <v>0.1134937410220714</v>
       </c>
       <c r="T26">
-        <v>0.6460363942282465</v>
+        <v>0.6546502128179565</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02157723283576863</v>
+        <v>0.02071414352233789</v>
       </c>
       <c r="W26">
-        <v>0.2307120884973258</v>
+        <v>0.2309156049574327</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.0863089313430746</v>
+        <v>0.08285657408935154</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1428492070059117</v>
+        <v>0.1447492070059118</v>
       </c>
       <c r="C27">
-        <v>157.2993018692088</v>
+        <v>146.0057732462888</v>
       </c>
       <c r="D27">
-        <v>294.7868018692088</v>
+        <v>289.1263732462888</v>
       </c>
       <c r="E27">
-        <v>139.1175</v>
+        <v>144.7506</v>
       </c>
       <c r="F27">
-        <v>140.8275</v>
+        <v>146.4606</v>
       </c>
       <c r="G27">
         <v>3.34</v>
@@ -3489,37 +3489,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M27">
-        <v>33.20712450000001</v>
+        <v>34.53540948000001</v>
       </c>
       <c r="N27">
-        <v>-30.45569592857143</v>
+        <v>-31.78398090857143</v>
       </c>
       <c r="O27">
-        <v>-7.613923982142858</v>
+        <v>-7.945995227142858</v>
       </c>
       <c r="P27">
-        <v>-22.84177194642858</v>
+        <v>-23.83798568142857</v>
       </c>
       <c r="Q27">
-        <v>-22.52177194642858</v>
+        <v>-23.51798568142857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1134937410220714</v>
+        <v>0.1144085213061535</v>
       </c>
       <c r="T27">
-        <v>0.6546502128179565</v>
+        <v>0.6634968373154965</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02071414352233789</v>
+        <v>0.01991744569455566</v>
       </c>
       <c r="W27">
-        <v>0.2309156049574327</v>
+        <v>0.2311034663052238</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.08285657408935154</v>
+        <v>0.07966978277822268</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1447492070059118</v>
+        <v>0.1466492070059118</v>
       </c>
       <c r="C28">
-        <v>146.0057732462888</v>
+        <v>134.9255296794013</v>
       </c>
       <c r="D28">
-        <v>289.1263732462888</v>
+        <v>283.6792296794014</v>
       </c>
       <c r="E28">
-        <v>144.7506</v>
+        <v>150.3837</v>
       </c>
       <c r="F28">
-        <v>146.4606</v>
+        <v>152.0937</v>
       </c>
       <c r="G28">
         <v>3.34</v>
@@ -3571,37 +3571,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M28">
-        <v>34.53540948000001</v>
+        <v>35.86369446</v>
       </c>
       <c r="N28">
-        <v>-31.78398090857143</v>
+        <v>-33.11226588857144</v>
       </c>
       <c r="O28">
-        <v>-7.945995227142858</v>
+        <v>-8.278066472142859</v>
       </c>
       <c r="P28">
-        <v>-23.83798568142857</v>
+        <v>-24.83419941642858</v>
       </c>
       <c r="Q28">
-        <v>-23.51798568142857</v>
+        <v>-24.51419941642857</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1144085213061535</v>
+        <v>0.115348364063772</v>
       </c>
       <c r="T28">
-        <v>0.6634968373154965</v>
+        <v>0.6725858350869417</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01991744569455566</v>
+        <v>0.01917976252068323</v>
       </c>
       <c r="W28">
-        <v>0.2311034663052238</v>
+        <v>0.2312774119976229</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.07966978277822268</v>
+        <v>0.07671905008273283</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1466492070059118</v>
+        <v>0.1485492070059117</v>
       </c>
       <c r="C29">
-        <v>134.9255296794013</v>
+        <v>124.0467392055095</v>
       </c>
       <c r="D29">
-        <v>283.6792296794014</v>
+        <v>278.4335392055096</v>
       </c>
       <c r="E29">
-        <v>150.3837</v>
+        <v>156.0168</v>
       </c>
       <c r="F29">
-        <v>152.0937</v>
+        <v>157.7268</v>
       </c>
       <c r="G29">
         <v>3.34</v>
@@ -3653,37 +3653,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M29">
-        <v>35.86369446</v>
+        <v>37.19197944</v>
       </c>
       <c r="N29">
-        <v>-33.11226588857144</v>
+        <v>-34.44055086857144</v>
       </c>
       <c r="O29">
-        <v>-8.278066472142859</v>
+        <v>-8.610137717142859</v>
       </c>
       <c r="P29">
-        <v>-24.83419941642858</v>
+        <v>-25.83041315142858</v>
       </c>
       <c r="Q29">
-        <v>-24.51419941642857</v>
+        <v>-25.51041315142858</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.115348364063772</v>
+        <v>0.1163143135646577</v>
       </c>
       <c r="T29">
-        <v>0.6725858350869417</v>
+        <v>0.6819273050187047</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01917976252068323</v>
+        <v>0.0184947710020874</v>
       </c>
       <c r="W29">
-        <v>0.2312774119976229</v>
+        <v>0.2314389329977078</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.07671905008273283</v>
+        <v>0.07397908400834952</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1485492070059117</v>
+        <v>0.1504492070059118</v>
       </c>
       <c r="C30">
-        <v>124.0467392055095</v>
+        <v>113.3584291410835</v>
       </c>
       <c r="D30">
-        <v>278.4335392055096</v>
+        <v>273.3783291410836</v>
       </c>
       <c r="E30">
-        <v>156.0168</v>
+        <v>161.6499</v>
       </c>
       <c r="F30">
-        <v>157.7268</v>
+        <v>163.3599</v>
       </c>
       <c r="G30">
         <v>3.34</v>
@@ -3735,37 +3735,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M30">
-        <v>37.19197944</v>
+        <v>38.52026442000001</v>
       </c>
       <c r="N30">
-        <v>-34.44055086857144</v>
+        <v>-35.76883584857144</v>
       </c>
       <c r="O30">
-        <v>-8.610137717142859</v>
+        <v>-8.94220896214286</v>
       </c>
       <c r="P30">
-        <v>-25.83041315142858</v>
+        <v>-26.82662688642858</v>
       </c>
       <c r="Q30">
-        <v>-25.51041315142858</v>
+        <v>-26.50662688642858</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1163143135646577</v>
+        <v>0.1173074729106388</v>
       </c>
       <c r="T30">
-        <v>0.6819273050187047</v>
+        <v>0.6915319149485456</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0184947710020874</v>
+        <v>0.01785702027787749</v>
       </c>
       <c r="W30">
-        <v>0.2314389329977078</v>
+        <v>0.2315893146184765</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.07397908400834952</v>
+        <v>0.07142808111150989</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1504492070059117</v>
+        <v>0.1523492070059118</v>
       </c>
       <c r="C31">
-        <v>113.3584291410836</v>
+        <v>102.850409468155</v>
       </c>
       <c r="D31">
-        <v>273.3783291410837</v>
+        <v>268.5034094681551</v>
       </c>
       <c r="E31">
-        <v>161.6499</v>
+        <v>167.283</v>
       </c>
       <c r="F31">
-        <v>163.3599</v>
+        <v>168.993</v>
       </c>
       <c r="G31">
         <v>3.34</v>
@@ -3817,37 +3817,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M31">
-        <v>38.52026442</v>
+        <v>39.84854940000001</v>
       </c>
       <c r="N31">
-        <v>-35.76883584857143</v>
+        <v>-37.09712082857144</v>
       </c>
       <c r="O31">
-        <v>-8.942208962142859</v>
+        <v>-9.27428020714286</v>
       </c>
       <c r="P31">
-        <v>-26.82662688642858</v>
+        <v>-27.82284062142858</v>
       </c>
       <c r="Q31">
-        <v>-26.50662688642858</v>
+        <v>-27.50284062142858</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1173074729106388</v>
+        <v>0.1183290082379337</v>
       </c>
       <c r="T31">
-        <v>0.6915319149485456</v>
+        <v>0.7014109423049535</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.01785702027787749</v>
+        <v>0.0172617862686149</v>
       </c>
       <c r="W31">
-        <v>0.2315893146184765</v>
+        <v>0.2317296707978606</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.07142808111150989</v>
+        <v>0.06904714507445953</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1523492070059118</v>
+        <v>0.1542492070059118</v>
       </c>
       <c r="C32">
-        <v>102.850409468155</v>
+        <v>92.51320427389862</v>
       </c>
       <c r="D32">
-        <v>268.5034094681551</v>
+        <v>263.7993042738987</v>
       </c>
       <c r="E32">
-        <v>167.283</v>
+        <v>172.9161</v>
       </c>
       <c r="F32">
-        <v>168.993</v>
+        <v>174.6261</v>
       </c>
       <c r="G32">
         <v>3.34</v>
@@ -3899,37 +3899,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M32">
-        <v>39.84854940000001</v>
+        <v>41.17683438</v>
       </c>
       <c r="N32">
-        <v>-37.09712082857144</v>
+        <v>-38.42540580857143</v>
       </c>
       <c r="O32">
-        <v>-9.27428020714286</v>
+        <v>-9.606351452142858</v>
       </c>
       <c r="P32">
-        <v>-27.82284062142858</v>
+        <v>-28.81905435642857</v>
       </c>
       <c r="Q32">
-        <v>-27.50284062142858</v>
+        <v>-28.49905435642857</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1183290082379337</v>
+        <v>0.1193801532848603</v>
       </c>
       <c r="T32">
-        <v>0.7014109423049535</v>
+        <v>0.7115763182803876</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0172617862686149</v>
+        <v>0.0167049544534983</v>
       </c>
       <c r="W32">
-        <v>0.2317296707978606</v>
+        <v>0.2318609717398651</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.06904714507445953</v>
+        <v>0.06681981781399315</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1542492070059118</v>
+        <v>0.1561492070059117</v>
       </c>
       <c r="C33">
-        <v>92.51320427389862</v>
+        <v>82.33799027308351</v>
       </c>
       <c r="D33">
-        <v>263.7993042738987</v>
+        <v>259.2571902730836</v>
       </c>
       <c r="E33">
-        <v>172.9161</v>
+        <v>178.5492</v>
       </c>
       <c r="F33">
-        <v>174.6261</v>
+        <v>180.2592</v>
       </c>
       <c r="G33">
         <v>3.34</v>
@@ -3981,37 +3981,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M33">
-        <v>41.17683438</v>
+        <v>42.50511936000001</v>
       </c>
       <c r="N33">
-        <v>-38.42540580857143</v>
+        <v>-39.75369078857144</v>
       </c>
       <c r="O33">
-        <v>-9.606351452142858</v>
+        <v>-9.93842269714286</v>
       </c>
       <c r="P33">
-        <v>-28.81905435642857</v>
+        <v>-29.81526809142858</v>
       </c>
       <c r="Q33">
-        <v>-28.49905435642857</v>
+        <v>-29.49526809142858</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1193801532848603</v>
+        <v>0.1204622143625788</v>
       </c>
       <c r="T33">
-        <v>0.7115763182803876</v>
+        <v>0.7220406759021579</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0167049544534983</v>
+        <v>0.01618292462682647</v>
       </c>
       <c r="W33">
-        <v>0.2318609717398651</v>
+        <v>0.2319840663729943</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.06681981781399315</v>
+        <v>0.06473169850730587</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1561492070059117</v>
+        <v>0.1580492070059117</v>
       </c>
       <c r="C34">
-        <v>82.33799027308351</v>
+        <v>72.31654157416648</v>
       </c>
       <c r="D34">
-        <v>259.2571902730836</v>
+        <v>254.8688415741665</v>
       </c>
       <c r="E34">
-        <v>178.5492</v>
+        <v>184.1823</v>
       </c>
       <c r="F34">
-        <v>180.2592</v>
+        <v>185.8923</v>
       </c>
       <c r="G34">
         <v>3.34</v>
@@ -4063,37 +4063,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M34">
-        <v>42.50511936000001</v>
+        <v>43.83340434000001</v>
       </c>
       <c r="N34">
-        <v>-39.75369078857144</v>
+        <v>-41.08197576857144</v>
       </c>
       <c r="O34">
-        <v>-9.93842269714286</v>
+        <v>-10.27049394214286</v>
       </c>
       <c r="P34">
-        <v>-29.81526809142858</v>
+        <v>-30.81148182642858</v>
       </c>
       <c r="Q34">
-        <v>-29.49526809142858</v>
+        <v>-30.49148182642858</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1204622143625788</v>
+        <v>0.1215765757709755</v>
       </c>
       <c r="T34">
-        <v>0.7220406759021579</v>
+        <v>0.7328174024081604</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.01618292462682647</v>
+        <v>0.0156925329714681</v>
       </c>
       <c r="W34">
-        <v>0.2319840663729943</v>
+        <v>0.2320997007253278</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.06473169850730587</v>
+        <v>0.06277013188587233</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1580492070059117</v>
+        <v>0.1599492070059118</v>
       </c>
       <c r="C35">
-        <v>72.31654157416648</v>
+        <v>62.44117996155759</v>
       </c>
       <c r="D35">
-        <v>254.8688415741665</v>
+        <v>250.6265799615576</v>
       </c>
       <c r="E35">
-        <v>184.1823</v>
+        <v>189.8154</v>
       </c>
       <c r="F35">
-        <v>185.8923</v>
+        <v>191.5254</v>
       </c>
       <c r="G35">
         <v>3.34</v>
@@ -4145,37 +4145,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M35">
-        <v>43.83340434000001</v>
+        <v>45.16168932000001</v>
       </c>
       <c r="N35">
-        <v>-41.08197576857144</v>
+        <v>-42.41026074857145</v>
       </c>
       <c r="O35">
-        <v>-10.27049394214286</v>
+        <v>-10.60256518714286</v>
       </c>
       <c r="P35">
-        <v>-30.81148182642858</v>
+        <v>-31.80769556142858</v>
       </c>
       <c r="Q35">
-        <v>-30.49148182642858</v>
+        <v>-31.48769556142858</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1215765757709755</v>
+        <v>0.1227247057068994</v>
       </c>
       <c r="T35">
-        <v>0.7328174024081604</v>
+        <v>0.7439206963840416</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0156925329714681</v>
+        <v>0.01523098788407197</v>
       </c>
       <c r="W35">
-        <v>0.2320997007253278</v>
+        <v>0.2322085330569358</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.06277013188587233</v>
+        <v>0.06092395153628782</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1599492070059118</v>
+        <v>0.1618492070059118</v>
       </c>
       <c r="C36">
-        <v>62.44117996155759</v>
+        <v>52.70473006186637</v>
       </c>
       <c r="D36">
-        <v>250.6265799615576</v>
+        <v>246.5232300618664</v>
       </c>
       <c r="E36">
-        <v>189.8154</v>
+        <v>195.4485</v>
       </c>
       <c r="F36">
-        <v>191.5254</v>
+        <v>197.1585</v>
       </c>
       <c r="G36">
         <v>3.34</v>
@@ -4227,37 +4227,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M36">
-        <v>45.16168932000001</v>
+        <v>46.48997430000001</v>
       </c>
       <c r="N36">
-        <v>-42.41026074857145</v>
+        <v>-43.73854572857144</v>
       </c>
       <c r="O36">
-        <v>-10.60256518714286</v>
+        <v>-10.93463643214286</v>
       </c>
       <c r="P36">
-        <v>-31.80769556142858</v>
+        <v>-32.80390929642858</v>
       </c>
       <c r="Q36">
-        <v>-31.48769556142858</v>
+        <v>-32.48390929642858</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1227247057068994</v>
+        <v>0.1239081627177747</v>
       </c>
       <c r="T36">
-        <v>0.7439206963840416</v>
+        <v>0.7553656301745653</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01523098788407197</v>
+        <v>0.01479581680166992</v>
       </c>
       <c r="W36">
-        <v>0.2322085330569358</v>
+        <v>0.2323111463981662</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.06092395153628782</v>
+        <v>0.05918326720667966</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1618492070059118</v>
+        <v>0.1637492070059118</v>
       </c>
       <c r="C37">
-        <v>52.70473006186637</v>
+        <v>43.10047884340943</v>
       </c>
       <c r="D37">
-        <v>246.5232300618664</v>
+        <v>242.5520788434095</v>
       </c>
       <c r="E37">
-        <v>195.4485</v>
+        <v>201.0816</v>
       </c>
       <c r="F37">
-        <v>197.1585</v>
+        <v>202.7916</v>
       </c>
       <c r="G37">
         <v>3.34</v>
@@ -4309,37 +4309,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M37">
-        <v>46.48997430000001</v>
+        <v>47.81825928000001</v>
       </c>
       <c r="N37">
-        <v>-43.73854572857144</v>
+        <v>-45.06683070857144</v>
       </c>
       <c r="O37">
-        <v>-10.93463643214286</v>
+        <v>-11.26670767714286</v>
       </c>
       <c r="P37">
-        <v>-32.80390929642858</v>
+        <v>-33.80012303142858</v>
       </c>
       <c r="Q37">
-        <v>-32.48390929642858</v>
+        <v>-33.48012303142858</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1239081627177747</v>
+        <v>0.12512860276024</v>
       </c>
       <c r="T37">
-        <v>0.7553656301745653</v>
+        <v>0.7671682181460429</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01479581680166992</v>
+        <v>0.01438482189051242</v>
       </c>
       <c r="W37">
-        <v>0.2323111463981662</v>
+        <v>0.2324080589982172</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.05918326720667966</v>
+        <v>0.05753928756204962</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1637492070059118</v>
+        <v>0.1656492070059117</v>
       </c>
       <c r="C38">
-        <v>43.10047884340946</v>
+        <v>33.62213896810735</v>
       </c>
       <c r="D38">
-        <v>242.5520788434095</v>
+        <v>238.7068389681074</v>
       </c>
       <c r="E38">
-        <v>201.0816</v>
+        <v>206.7147</v>
       </c>
       <c r="F38">
-        <v>202.7916</v>
+        <v>208.4247</v>
       </c>
       <c r="G38">
         <v>3.34</v>
@@ -4391,37 +4391,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M38">
-        <v>47.81825928000001</v>
+        <v>49.14654426000001</v>
       </c>
       <c r="N38">
-        <v>-45.06683070857144</v>
+        <v>-46.39511568857144</v>
       </c>
       <c r="O38">
-        <v>-11.26670767714286</v>
+        <v>-11.59877892214286</v>
       </c>
       <c r="P38">
-        <v>-33.80012303142858</v>
+        <v>-34.79633676642858</v>
       </c>
       <c r="Q38">
-        <v>-33.48012303142858</v>
+        <v>-34.47633676642858</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.12512860276024</v>
+        <v>0.1263877869310374</v>
       </c>
       <c r="T38">
-        <v>0.7671682181460429</v>
+        <v>0.7793454914499482</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01438482189051242</v>
+        <v>0.01399604292049857</v>
       </c>
       <c r="W38">
-        <v>0.2324080589982172</v>
+        <v>0.2324997330793464</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.05753928756204962</v>
+        <v>0.05598417168199421</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1656492070059117</v>
+        <v>0.1675492070059117</v>
       </c>
       <c r="C39">
-        <v>33.62213896810735</v>
+        <v>24.26381557492843</v>
       </c>
       <c r="D39">
-        <v>238.7068389681074</v>
+        <v>234.9816155749284</v>
       </c>
       <c r="E39">
-        <v>206.7147</v>
+        <v>212.3478</v>
       </c>
       <c r="F39">
-        <v>208.4247</v>
+        <v>214.0578</v>
       </c>
       <c r="G39">
         <v>3.34</v>
@@ -4473,37 +4473,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M39">
-        <v>49.14654426000001</v>
+        <v>50.47482924000001</v>
       </c>
       <c r="N39">
-        <v>-46.39511568857144</v>
+        <v>-47.72340066857144</v>
       </c>
       <c r="O39">
-        <v>-11.59877892214286</v>
+        <v>-11.93085016714286</v>
       </c>
       <c r="P39">
-        <v>-34.79633676642858</v>
+        <v>-35.79255050142858</v>
       </c>
       <c r="Q39">
-        <v>-34.47633676642858</v>
+        <v>-35.47255050142858</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1263877869310374</v>
+        <v>0.1276875899460541</v>
       </c>
       <c r="T39">
-        <v>0.7793454914499482</v>
+        <v>0.7919155800217216</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01399604292049857</v>
+        <v>0.01362772600153808</v>
       </c>
       <c r="W39">
-        <v>0.2324997330793464</v>
+        <v>0.2325865822088373</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.05598417168199421</v>
+        <v>0.05451090400615233</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1675492070059117</v>
+        <v>0.1694492070059118</v>
       </c>
       <c r="C40">
-        <v>24.26381557492843</v>
+        <v>15.0199761257783</v>
       </c>
       <c r="D40">
-        <v>234.9816155749284</v>
+        <v>231.3708761257783</v>
       </c>
       <c r="E40">
-        <v>212.3478</v>
+        <v>217.9809</v>
       </c>
       <c r="F40">
-        <v>214.0578</v>
+        <v>219.6909</v>
       </c>
       <c r="G40">
         <v>3.34</v>
@@ -4555,37 +4555,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M40">
-        <v>50.47482924000001</v>
+        <v>51.80311422000001</v>
       </c>
       <c r="N40">
-        <v>-47.72340066857144</v>
+        <v>-49.05168564857144</v>
       </c>
       <c r="O40">
-        <v>-11.93085016714286</v>
+        <v>-12.26292141214286</v>
       </c>
       <c r="P40">
-        <v>-35.79255050142858</v>
+        <v>-36.78876423642858</v>
       </c>
       <c r="Q40">
-        <v>-35.47255050142858</v>
+        <v>-36.46876423642858</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1276875899460541</v>
+        <v>0.1290300094533665</v>
       </c>
       <c r="T40">
-        <v>0.7919155800217216</v>
+        <v>0.8048978026450286</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01362772600153808</v>
+        <v>0.01327829712970377</v>
       </c>
       <c r="W40">
-        <v>0.2325865822088373</v>
+        <v>0.2326689775368159</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.05451090400615233</v>
+        <v>0.05311318851881508</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1694492070059118</v>
+        <v>0.1713492070059118</v>
       </c>
       <c r="C41">
-        <v>15.0199761257783</v>
+        <v>5.885422989413428</v>
       </c>
       <c r="D41">
-        <v>231.3708761257783</v>
+        <v>227.8694229894135</v>
       </c>
       <c r="E41">
-        <v>217.9809</v>
+        <v>223.614</v>
       </c>
       <c r="F41">
-        <v>219.6909</v>
+        <v>225.324</v>
       </c>
       <c r="G41">
         <v>3.34</v>
@@ -4637,37 +4637,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M41">
-        <v>51.80311422000001</v>
+        <v>53.13139920000001</v>
       </c>
       <c r="N41">
-        <v>-49.05168564857144</v>
+        <v>-50.37997062857144</v>
       </c>
       <c r="O41">
-        <v>-12.26292141214286</v>
+        <v>-12.59499265714286</v>
       </c>
       <c r="P41">
-        <v>-36.78876423642858</v>
+        <v>-37.78497797142858</v>
       </c>
       <c r="Q41">
-        <v>-36.46876423642858</v>
+        <v>-37.46497797142858</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1290300094533665</v>
+        <v>0.1304171762775893</v>
       </c>
       <c r="T41">
-        <v>0.8048978026450286</v>
+        <v>0.8183127660224457</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01327829712970377</v>
+        <v>0.01294633970146118</v>
       </c>
       <c r="W41">
-        <v>0.2326689775368159</v>
+        <v>0.2327472530983954</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.05311318851881508</v>
+        <v>0.05178535880584467</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1713492070059118</v>
+        <v>0.1732492070059118</v>
       </c>
       <c r="C42">
-        <v>5.885422989413428</v>
+        <v>-3.144731522348366</v>
       </c>
       <c r="D42">
-        <v>227.8694229894135</v>
+        <v>224.4723684776517</v>
       </c>
       <c r="E42">
-        <v>223.614</v>
+        <v>229.2471</v>
       </c>
       <c r="F42">
-        <v>225.324</v>
+        <v>230.9571000000001</v>
       </c>
       <c r="G42">
         <v>3.34</v>
@@ -4719,37 +4719,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M42">
-        <v>53.13139920000001</v>
+        <v>54.45968418000002</v>
       </c>
       <c r="N42">
-        <v>-50.37997062857144</v>
+        <v>-51.70825560857145</v>
       </c>
       <c r="O42">
-        <v>-12.59499265714286</v>
+        <v>-12.92706390214286</v>
       </c>
       <c r="P42">
-        <v>-37.78497797142858</v>
+        <v>-38.78119170642859</v>
       </c>
       <c r="Q42">
-        <v>-37.46497797142858</v>
+        <v>-38.46119170642859</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1304171762775893</v>
+        <v>0.131851365706023</v>
       </c>
       <c r="T42">
-        <v>0.8183127660224457</v>
+        <v>0.8321824739211312</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01294633970146118</v>
+        <v>0.01263057531849871</v>
       </c>
       <c r="W42">
-        <v>0.2327472530983954</v>
+        <v>0.232821710339898</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.05178535880584467</v>
+        <v>0.05052230127399482</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1732492070059118</v>
+        <v>0.1751492070059117</v>
       </c>
       <c r="C43">
-        <v>-3.144731522348366</v>
+        <v>-12.07508791826916</v>
       </c>
       <c r="D43">
-        <v>224.4723684776517</v>
+        <v>221.1751120817309</v>
       </c>
       <c r="E43">
-        <v>229.2471</v>
+        <v>234.8802</v>
       </c>
       <c r="F43">
-        <v>230.9571000000001</v>
+        <v>236.5902</v>
       </c>
       <c r="G43">
         <v>3.34</v>
@@ -4801,37 +4801,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M43">
-        <v>54.45968418000002</v>
+        <v>55.78796916000001</v>
       </c>
       <c r="N43">
-        <v>-51.70825560857145</v>
+        <v>-53.03654058857144</v>
       </c>
       <c r="O43">
-        <v>-12.92706390214286</v>
+        <v>-13.25913514714286</v>
       </c>
       <c r="P43">
-        <v>-38.78119170642859</v>
+        <v>-39.77740544142858</v>
       </c>
       <c r="Q43">
-        <v>-38.46119170642859</v>
+        <v>-39.45740544142858</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.131851365706023</v>
+        <v>0.1333350099423337</v>
       </c>
       <c r="T43">
-        <v>0.8321824739211312</v>
+        <v>0.8465304476094265</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01263057531849871</v>
+        <v>0.01232984733472493</v>
       </c>
       <c r="W43">
-        <v>0.232821710339898</v>
+        <v>0.2328926219984719</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.05052230127399482</v>
+        <v>0.04931938933889968</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1751492070059117</v>
+        <v>0.1770492070059118</v>
       </c>
       <c r="C44">
-        <v>-12.07508791826913</v>
+        <v>-20.90998031413756</v>
       </c>
       <c r="D44">
-        <v>221.1751120817309</v>
+        <v>217.9733196858625</v>
       </c>
       <c r="E44">
-        <v>234.8802</v>
+        <v>240.5133</v>
       </c>
       <c r="F44">
-        <v>236.5902</v>
+        <v>242.2233</v>
       </c>
       <c r="G44">
         <v>3.34</v>
@@ -4883,37 +4883,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M44">
-        <v>55.78796916</v>
+        <v>57.11625414000001</v>
       </c>
       <c r="N44">
-        <v>-53.03654058857143</v>
+        <v>-54.36482556857144</v>
       </c>
       <c r="O44">
-        <v>-13.25913514714286</v>
+        <v>-13.59120639214286</v>
       </c>
       <c r="P44">
-        <v>-39.77740544142858</v>
+        <v>-40.77361917642858</v>
       </c>
       <c r="Q44">
-        <v>-39.45740544142858</v>
+        <v>-40.45361917642858</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1333350099423337</v>
+        <v>0.1348707118711466</v>
       </c>
       <c r="T44">
-        <v>0.8465304476094265</v>
+        <v>0.8613818589709954</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01232984733472493</v>
+        <v>0.01204310669903366</v>
       </c>
       <c r="W44">
-        <v>0.2328926219984719</v>
+        <v>0.2329602354403679</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.04931938933889968</v>
+        <v>0.04817242679613454</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1770492070059118</v>
+        <v>0.1789492070059118</v>
       </c>
       <c r="C45">
-        <v>-20.90998031413756</v>
+        <v>-29.65349543951456</v>
       </c>
       <c r="D45">
-        <v>217.9733196858625</v>
+        <v>214.8629045604855</v>
       </c>
       <c r="E45">
-        <v>240.5133</v>
+        <v>246.1464</v>
       </c>
       <c r="F45">
-        <v>242.2233</v>
+        <v>247.8564</v>
       </c>
       <c r="G45">
         <v>3.34</v>
@@ -4965,37 +4965,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M45">
-        <v>57.11625414000001</v>
+        <v>58.44453912000001</v>
       </c>
       <c r="N45">
-        <v>-54.36482556857144</v>
+        <v>-55.69311054857144</v>
       </c>
       <c r="O45">
-        <v>-13.59120639214286</v>
+        <v>-13.92327763714286</v>
       </c>
       <c r="P45">
-        <v>-40.77361917642858</v>
+        <v>-41.76983291142858</v>
       </c>
       <c r="Q45">
-        <v>-40.45361917642858</v>
+        <v>-41.44983291142858</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1348707118711466</v>
+        <v>0.1364612602974171</v>
       </c>
       <c r="T45">
-        <v>0.8613818589709954</v>
+        <v>0.8767636778811918</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01204310669903366</v>
+        <v>0.01176939972860107</v>
       </c>
       <c r="W45">
-        <v>0.2329602354403679</v>
+        <v>0.2330247755439959</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.04817242679613454</v>
+        <v>0.04707759891440422</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1789492070059118</v>
+        <v>0.1808492070059118</v>
       </c>
       <c r="C46">
-        <v>-29.65349543951456</v>
+        <v>-38.30949004005123</v>
       </c>
       <c r="D46">
-        <v>214.8629045604855</v>
+        <v>211.8400099599488</v>
       </c>
       <c r="E46">
-        <v>246.1464</v>
+        <v>251.7795</v>
       </c>
       <c r="F46">
-        <v>247.8564</v>
+        <v>253.4895</v>
       </c>
       <c r="G46">
         <v>3.34</v>
@@ -5047,37 +5047,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M46">
-        <v>58.44453912000001</v>
+        <v>59.77282410000001</v>
       </c>
       <c r="N46">
-        <v>-55.69311054857144</v>
+        <v>-57.02139552857144</v>
       </c>
       <c r="O46">
-        <v>-13.92327763714286</v>
+        <v>-14.25534888214286</v>
       </c>
       <c r="P46">
-        <v>-41.76983291142858</v>
+        <v>-42.76604664642858</v>
       </c>
       <c r="Q46">
-        <v>-41.44983291142858</v>
+        <v>-42.44604664642858</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1364612602974171</v>
+        <v>0.1381096468482793</v>
       </c>
       <c r="T46">
-        <v>0.8767636778811918</v>
+        <v>0.8927048356608499</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01176939972860107</v>
+        <v>0.01150785751240994</v>
       </c>
       <c r="W46">
-        <v>0.2330247755439959</v>
+        <v>0.2330864471985737</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.04707759891440422</v>
+        <v>0.04603143004963972</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1808492070059118</v>
+        <v>0.1827492070059118</v>
       </c>
       <c r="C47">
-        <v>-38.30949004005123</v>
+        <v>-46.88160683119287</v>
       </c>
       <c r="D47">
-        <v>211.8400099599488</v>
+        <v>208.9009931688072</v>
       </c>
       <c r="E47">
-        <v>251.7795</v>
+        <v>257.4126000000001</v>
       </c>
       <c r="F47">
-        <v>253.4895</v>
+        <v>259.1226</v>
       </c>
       <c r="G47">
         <v>3.34</v>
@@ -5129,37 +5129,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M47">
-        <v>59.77282410000001</v>
+        <v>61.10110908000001</v>
       </c>
       <c r="N47">
-        <v>-57.02139552857144</v>
+        <v>-58.34968050857144</v>
       </c>
       <c r="O47">
-        <v>-14.25534888214286</v>
+        <v>-14.58742012714286</v>
       </c>
       <c r="P47">
-        <v>-42.76604664642858</v>
+        <v>-43.76226038142858</v>
       </c>
       <c r="Q47">
-        <v>-42.44604664642858</v>
+        <v>-43.44226038142858</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1381096468482793</v>
+        <v>0.139819084752877</v>
       </c>
       <c r="T47">
-        <v>0.8927048356608499</v>
+        <v>0.9092364066916064</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01150785751240994</v>
+        <v>0.01125768669692277</v>
       </c>
       <c r="W47">
-        <v>0.2330864471985737</v>
+        <v>0.2331454374768656</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.04603143004963972</v>
+        <v>0.04503074678769103</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1827492070059118</v>
+        <v>0.1846492070059118</v>
       </c>
       <c r="C48">
-        <v>-46.88160683119287</v>
+        <v>-55.37328914202902</v>
       </c>
       <c r="D48">
-        <v>208.9009931688072</v>
+        <v>206.042410857971</v>
       </c>
       <c r="E48">
-        <v>257.4126000000001</v>
+        <v>263.0457000000001</v>
       </c>
       <c r="F48">
-        <v>259.1226</v>
+        <v>264.7557</v>
       </c>
       <c r="G48">
         <v>3.34</v>
@@ -5211,37 +5211,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M48">
-        <v>61.10110908000001</v>
+        <v>62.42939406000001</v>
       </c>
       <c r="N48">
-        <v>-58.34968050857144</v>
+        <v>-59.67796548857145</v>
       </c>
       <c r="O48">
-        <v>-14.58742012714286</v>
+        <v>-14.91949137214286</v>
       </c>
       <c r="P48">
-        <v>-43.76226038142858</v>
+        <v>-44.75847411642859</v>
       </c>
       <c r="Q48">
-        <v>-43.44226038142858</v>
+        <v>-44.43847411642859</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.139819084752877</v>
+        <v>0.1415930297482143</v>
       </c>
       <c r="T48">
-        <v>0.9092364066916064</v>
+        <v>0.926391810591448</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01125768669692277</v>
+        <v>0.01101816144805207</v>
       </c>
       <c r="W48">
-        <v>0.2331454374768656</v>
+        <v>0.2332019175305493</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.04503074678769103</v>
+        <v>0.04407264579220826</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1846492070059118</v>
+        <v>0.1865492070059118</v>
       </c>
       <c r="C49">
-        <v>-55.37328914202902</v>
+        <v>-63.78779437306312</v>
       </c>
       <c r="D49">
-        <v>206.042410857971</v>
+        <v>203.2610056269369</v>
       </c>
       <c r="E49">
-        <v>263.0457000000001</v>
+        <v>268.6788000000001</v>
       </c>
       <c r="F49">
-        <v>264.7557</v>
+        <v>270.3888000000001</v>
       </c>
       <c r="G49">
         <v>3.34</v>
@@ -5293,37 +5293,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M49">
-        <v>62.42939406000001</v>
+        <v>63.75767904000001</v>
       </c>
       <c r="N49">
-        <v>-59.67796548857145</v>
+        <v>-61.00625046857144</v>
       </c>
       <c r="O49">
-        <v>-14.91949137214286</v>
+        <v>-15.25156261714286</v>
       </c>
       <c r="P49">
-        <v>-44.75847411642859</v>
+        <v>-45.75468785142859</v>
       </c>
       <c r="Q49">
-        <v>-44.43847411642859</v>
+        <v>-45.43468785142858</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1415930297482143</v>
+        <v>0.1434352033972184</v>
       </c>
       <c r="T49">
-        <v>0.926391810591448</v>
+        <v>0.9442070377182065</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01101816144805207</v>
+        <v>0.01078861641788431</v>
       </c>
       <c r="W49">
-        <v>0.2332019175305493</v>
+        <v>0.2332560442486629</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.04407264579220826</v>
+        <v>0.04315446567153725</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1865492070059118</v>
+        <v>0.1884492070059118</v>
       </c>
       <c r="C50">
-        <v>-63.78779437306306</v>
+        <v>-72.12820637848614</v>
       </c>
       <c r="D50">
-        <v>203.2610056269369</v>
+        <v>200.5536936215139</v>
       </c>
       <c r="E50">
-        <v>268.6788</v>
+        <v>274.3119</v>
       </c>
       <c r="F50">
-        <v>270.3888</v>
+        <v>276.0219</v>
       </c>
       <c r="G50">
         <v>3.34</v>
@@ -5375,37 +5375,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M50">
-        <v>63.75767904000001</v>
+        <v>65.08596402000001</v>
       </c>
       <c r="N50">
-        <v>-61.00625046857144</v>
+        <v>-62.33453544857144</v>
       </c>
       <c r="O50">
-        <v>-15.25156261714286</v>
+        <v>-15.58363386214286</v>
       </c>
       <c r="P50">
-        <v>-45.75468785142858</v>
+        <v>-46.75090158642858</v>
       </c>
       <c r="Q50">
-        <v>-45.43468785142858</v>
+        <v>-46.43090158642858</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1434352033972184</v>
+        <v>0.1453496191501051</v>
       </c>
       <c r="T50">
-        <v>0.9442070377182065</v>
+        <v>0.9627209012028772</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01078861641788432</v>
+        <v>0.01056844057262137</v>
       </c>
       <c r="W50">
-        <v>0.2332560442486629</v>
+        <v>0.2333079617129759</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.04315446567153725</v>
+        <v>0.04227376229048541</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1884492070059118</v>
+        <v>0.1903492070059118</v>
       </c>
       <c r="C51">
-        <v>-72.12820637848614</v>
+        <v>-80.397446871912</v>
       </c>
       <c r="D51">
-        <v>200.5536936215139</v>
+        <v>197.917553128088</v>
       </c>
       <c r="E51">
-        <v>274.3119</v>
+        <v>279.9450000000001</v>
       </c>
       <c r="F51">
-        <v>276.0219</v>
+        <v>281.655</v>
       </c>
       <c r="G51">
         <v>3.34</v>
@@ -5457,37 +5457,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M51">
-        <v>65.08596402000001</v>
+        <v>66.41424900000001</v>
       </c>
       <c r="N51">
-        <v>-62.33453544857144</v>
+        <v>-63.66282042857144</v>
       </c>
       <c r="O51">
-        <v>-15.58363386214286</v>
+        <v>-15.91570510714286</v>
       </c>
       <c r="P51">
-        <v>-46.75090158642858</v>
+        <v>-47.74711532142858</v>
       </c>
       <c r="Q51">
-        <v>-46.43090158642858</v>
+        <v>-47.42711532142858</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1453496191501051</v>
+        <v>0.1473406115331072</v>
       </c>
       <c r="T51">
-        <v>0.9627209012028772</v>
+        <v>0.9819753192269348</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01056844057262137</v>
+        <v>0.01035707176116894</v>
       </c>
       <c r="W51">
-        <v>0.2333079617129759</v>
+        <v>0.2333578024787164</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.04227376229048541</v>
+        <v>0.04142828704467572</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1903492070059118</v>
+        <v>0.1922492070059118</v>
       </c>
       <c r="C52">
-        <v>-80.397446871912</v>
+        <v>-88.59828594425937</v>
       </c>
       <c r="D52">
-        <v>197.917553128088</v>
+        <v>195.3498140557407</v>
       </c>
       <c r="E52">
-        <v>279.9450000000001</v>
+        <v>285.5781000000001</v>
       </c>
       <c r="F52">
-        <v>281.655</v>
+        <v>287.2881</v>
       </c>
       <c r="G52">
         <v>3.34</v>
@@ -5539,37 +5539,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M52">
-        <v>66.41424900000001</v>
+        <v>67.74253398000002</v>
       </c>
       <c r="N52">
-        <v>-63.66282042857144</v>
+        <v>-64.99110540857144</v>
       </c>
       <c r="O52">
-        <v>-15.91570510714286</v>
+        <v>-16.24777635214286</v>
       </c>
       <c r="P52">
-        <v>-47.74711532142858</v>
+        <v>-48.74332905642858</v>
       </c>
       <c r="Q52">
-        <v>-47.42711532142858</v>
+        <v>-48.42332905642858</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1473406115331072</v>
+        <v>0.1494128689113338</v>
       </c>
       <c r="T52">
-        <v>0.9819753192269348</v>
+        <v>1.002015631864219</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01035707176116894</v>
+        <v>0.01015399192271465</v>
       </c>
       <c r="W52">
-        <v>0.2333578024787164</v>
+        <v>0.2334056887046239</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.04142828704467572</v>
+        <v>0.04061596769085862</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1922492070059118</v>
+        <v>0.1941492070059118</v>
       </c>
       <c r="C53">
-        <v>-88.59828594425937</v>
+        <v>-96.73335177337978</v>
       </c>
       <c r="D53">
-        <v>195.3498140557407</v>
+        <v>192.8478482266203</v>
       </c>
       <c r="E53">
-        <v>285.5781000000001</v>
+        <v>291.2112000000001</v>
       </c>
       <c r="F53">
-        <v>287.2881</v>
+        <v>292.9212000000001</v>
       </c>
       <c r="G53">
         <v>3.34</v>
@@ -5621,37 +5621,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M53">
-        <v>67.74253398000002</v>
+        <v>69.07081896000001</v>
       </c>
       <c r="N53">
-        <v>-64.99110540857144</v>
+        <v>-66.31939038857143</v>
       </c>
       <c r="O53">
-        <v>-16.24777635214286</v>
+        <v>-16.57984759714286</v>
       </c>
       <c r="P53">
-        <v>-48.74332905642858</v>
+        <v>-49.73954279142858</v>
       </c>
       <c r="Q53">
-        <v>-48.42332905642858</v>
+        <v>-49.41954279142858</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1494128689113338</v>
+        <v>0.1515714703469866</v>
       </c>
       <c r="T53">
-        <v>1.002015631864219</v>
+        <v>1.022890957528057</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01015399192271465</v>
+        <v>0.009958722847277829</v>
       </c>
       <c r="W53">
-        <v>0.2334056887046239</v>
+        <v>0.2334517331526119</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.04061596769085862</v>
+        <v>0.03983489138911134</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1941492070059118</v>
+        <v>0.1960492070059118</v>
       </c>
       <c r="C54">
-        <v>-96.73335177337978</v>
+        <v>-104.8051395969779</v>
       </c>
       <c r="D54">
-        <v>192.8478482266203</v>
+        <v>190.4091604030222</v>
       </c>
       <c r="E54">
-        <v>291.2112000000001</v>
+        <v>296.8443000000001</v>
       </c>
       <c r="F54">
-        <v>292.9212000000001</v>
+        <v>298.5543000000001</v>
       </c>
       <c r="G54">
         <v>3.34</v>
@@ -5703,37 +5703,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M54">
-        <v>69.07081896000001</v>
+        <v>70.39910394000002</v>
       </c>
       <c r="N54">
-        <v>-66.31939038857143</v>
+        <v>-67.64767536857144</v>
       </c>
       <c r="O54">
-        <v>-16.57984759714286</v>
+        <v>-16.91191884214286</v>
       </c>
       <c r="P54">
-        <v>-49.73954279142858</v>
+        <v>-50.73575652642858</v>
       </c>
       <c r="Q54">
-        <v>-49.41954279142858</v>
+        <v>-50.41575652642858</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1515714703469866</v>
+        <v>0.15382192716288</v>
       </c>
       <c r="T54">
-        <v>1.022890957528057</v>
+        <v>1.044654594922271</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.009958722847277829</v>
+        <v>0.009770822416197115</v>
       </c>
       <c r="W54">
-        <v>0.2334517331526119</v>
+        <v>0.2334960400742607</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.03983489138911134</v>
+        <v>0.03908328966478858</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1960492070059118</v>
+        <v>0.1979492070059117</v>
       </c>
       <c r="C55">
-        <v>-104.8051395969779</v>
+        <v>-112.816020013222</v>
       </c>
       <c r="D55">
-        <v>190.4091604030222</v>
+        <v>188.0313799867781</v>
       </c>
       <c r="E55">
-        <v>296.8443000000001</v>
+        <v>302.4774</v>
       </c>
       <c r="F55">
-        <v>298.5543000000001</v>
+        <v>304.1874</v>
       </c>
       <c r="G55">
         <v>3.34</v>
@@ -5785,37 +5785,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M55">
-        <v>70.39910394000002</v>
+        <v>71.72738892000001</v>
       </c>
       <c r="N55">
-        <v>-67.64767536857144</v>
+        <v>-68.97596034857143</v>
       </c>
       <c r="O55">
-        <v>-16.91191884214286</v>
+        <v>-17.24399008714286</v>
       </c>
       <c r="P55">
-        <v>-50.73575652642858</v>
+        <v>-51.73197026142857</v>
       </c>
       <c r="Q55">
-        <v>-50.41575652642858</v>
+        <v>-51.41197026142857</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.15382192716288</v>
+        <v>0.1561702299272904</v>
       </c>
       <c r="T55">
-        <v>1.044654594922271</v>
+        <v>1.067364477420581</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.009770822416197115</v>
+        <v>0.009589881260341614</v>
       </c>
       <c r="W55">
-        <v>0.2334960400742607</v>
+        <v>0.2335387059988114</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.03908328966478858</v>
+        <v>0.03835952504136653</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1979492070059117</v>
+        <v>0.1998492070059118</v>
       </c>
       <c r="C56">
-        <v>-112.816020013222</v>
+        <v>-120.7682466670917</v>
       </c>
       <c r="D56">
-        <v>188.0313799867781</v>
+        <v>185.7122533329084</v>
       </c>
       <c r="E56">
-        <v>302.4774</v>
+        <v>308.1105000000001</v>
       </c>
       <c r="F56">
-        <v>304.1874</v>
+        <v>309.8205</v>
       </c>
       <c r="G56">
         <v>3.34</v>
@@ -5867,37 +5867,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M56">
-        <v>71.72738892000001</v>
+        <v>73.05567390000002</v>
       </c>
       <c r="N56">
-        <v>-68.97596034857143</v>
+        <v>-70.30424532857144</v>
       </c>
       <c r="O56">
-        <v>-17.24399008714286</v>
+        <v>-17.57606133214286</v>
       </c>
       <c r="P56">
-        <v>-51.73197026142857</v>
+        <v>-52.72818399642858</v>
       </c>
       <c r="Q56">
-        <v>-51.41197026142857</v>
+        <v>-52.40818399642858</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1561702299272904</v>
+        <v>0.1586229017034524</v>
       </c>
       <c r="T56">
-        <v>1.067364477420581</v>
+        <v>1.091083688029928</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.009589881260341614</v>
+        <v>0.009415519782880856</v>
       </c>
       <c r="W56">
-        <v>0.2335387059988114</v>
+        <v>0.2335798204351967</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.03835952504136653</v>
+        <v>0.03766207913152353</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1998492070059118</v>
+        <v>0.2017492070059118</v>
       </c>
       <c r="C57">
-        <v>-120.7682466670917</v>
+        <v>-128.6639633748454</v>
       </c>
       <c r="D57">
-        <v>185.7122533329084</v>
+        <v>183.4496366251546</v>
       </c>
       <c r="E57">
-        <v>308.1105000000001</v>
+        <v>313.7436000000001</v>
       </c>
       <c r="F57">
-        <v>309.8205</v>
+        <v>315.4536000000001</v>
       </c>
       <c r="G57">
         <v>3.34</v>
@@ -5949,37 +5949,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M57">
-        <v>73.05567390000002</v>
+        <v>74.38395888000001</v>
       </c>
       <c r="N57">
-        <v>-70.30424532857144</v>
+        <v>-71.63253030857143</v>
       </c>
       <c r="O57">
-        <v>-17.57606133214286</v>
+        <v>-17.90813257714286</v>
       </c>
       <c r="P57">
-        <v>-52.72818399642858</v>
+        <v>-53.72439773142857</v>
       </c>
       <c r="Q57">
-        <v>-52.40818399642858</v>
+        <v>-53.40439773142857</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1586229017034524</v>
+        <v>0.161187058560349</v>
       </c>
       <c r="T57">
-        <v>1.091083688029928</v>
+        <v>1.115881044576062</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.009415519782880856</v>
+        <v>0.0092473855010437</v>
       </c>
       <c r="W57">
-        <v>0.2335798204351967</v>
+        <v>0.2336194664988539</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.03766207913152353</v>
+        <v>0.03698954200417481</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2017492070059118</v>
+        <v>0.2036492070059118</v>
       </c>
       <c r="C58">
-        <v>-128.6639633748454</v>
+        <v>-136.5052107339559</v>
       </c>
       <c r="D58">
-        <v>183.4496366251546</v>
+        <v>181.2414892660442</v>
       </c>
       <c r="E58">
-        <v>313.7436000000001</v>
+        <v>319.3767000000001</v>
       </c>
       <c r="F58">
-        <v>315.4536000000001</v>
+        <v>321.0867000000001</v>
       </c>
       <c r="G58">
         <v>3.34</v>
@@ -6031,37 +6031,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M58">
-        <v>74.38395888000001</v>
+        <v>75.71224386000002</v>
       </c>
       <c r="N58">
-        <v>-71.63253030857143</v>
+        <v>-72.96081528857144</v>
       </c>
       <c r="O58">
-        <v>-17.90813257714286</v>
+        <v>-18.24020382214286</v>
       </c>
       <c r="P58">
-        <v>-53.72439773142857</v>
+        <v>-54.72061146642858</v>
       </c>
       <c r="Q58">
-        <v>-53.40439773142857</v>
+        <v>-54.40061146642858</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.161187058560349</v>
+        <v>0.1638704785268688</v>
       </c>
       <c r="T58">
-        <v>1.115881044576062</v>
+        <v>1.141831766542948</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0092473855010437</v>
+        <v>0.009085150667692055</v>
       </c>
       <c r="W58">
-        <v>0.2336194664988539</v>
+        <v>0.2336577214725582</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.03698954200417481</v>
+        <v>0.03634060267076833</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2036492070059118</v>
+        <v>0.2055492070059118</v>
       </c>
       <c r="C59">
-        <v>-136.5052107339559</v>
+        <v>-144.2939322613463</v>
       </c>
       <c r="D59">
-        <v>181.2414892660442</v>
+        <v>179.0858677386537</v>
       </c>
       <c r="E59">
-        <v>319.3767000000001</v>
+        <v>325.0098000000001</v>
       </c>
       <c r="F59">
-        <v>321.0867000000001</v>
+        <v>326.7198000000001</v>
       </c>
       <c r="G59">
         <v>3.34</v>
@@ -6113,37 +6113,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M59">
-        <v>75.71224386000002</v>
+        <v>77.04052884000002</v>
       </c>
       <c r="N59">
-        <v>-72.96081528857144</v>
+        <v>-74.28910026857145</v>
       </c>
       <c r="O59">
-        <v>-18.24020382214286</v>
+        <v>-18.57227506714286</v>
       </c>
       <c r="P59">
-        <v>-54.72061146642858</v>
+        <v>-55.71682520142858</v>
       </c>
       <c r="Q59">
-        <v>-54.40061146642858</v>
+        <v>-55.39682520142858</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1638704785268688</v>
+        <v>0.1666816803965562</v>
       </c>
       <c r="T59">
-        <v>1.141831766542948</v>
+        <v>1.169018237174923</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.009085150667692055</v>
+        <v>0.008928510138938743</v>
       </c>
       <c r="W59">
-        <v>0.2336577214725582</v>
+        <v>0.2336946573092383</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.03634060267076833</v>
+        <v>0.035714040555755</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2055492070059118</v>
+        <v>0.2074492070059118</v>
       </c>
       <c r="C60">
-        <v>-144.2939322613463</v>
+        <v>-152.0319800987396</v>
       </c>
       <c r="D60">
-        <v>179.0858677386537</v>
+        <v>176.9809199012604</v>
       </c>
       <c r="E60">
-        <v>325.0098</v>
+        <v>330.6429000000001</v>
       </c>
       <c r="F60">
-        <v>326.7198</v>
+        <v>332.3529</v>
       </c>
       <c r="G60">
         <v>3.34</v>
@@ -6195,37 +6195,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M60">
-        <v>77.04052884000001</v>
+        <v>78.36881382000001</v>
       </c>
       <c r="N60">
-        <v>-74.28910026857143</v>
+        <v>-75.61738524857144</v>
       </c>
       <c r="O60">
-        <v>-18.57227506714286</v>
+        <v>-18.90434631214286</v>
       </c>
       <c r="P60">
-        <v>-55.71682520142858</v>
+        <v>-56.71303893642857</v>
       </c>
       <c r="Q60">
-        <v>-55.39682520142858</v>
+        <v>-56.39303893642857</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1666816803965561</v>
+        <v>0.1696300140647648</v>
       </c>
       <c r="T60">
-        <v>1.169018237174922</v>
+        <v>1.197530877106018</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.008928510138938745</v>
+        <v>0.008777179458617747</v>
       </c>
       <c r="W60">
-        <v>0.2336946573092383</v>
+        <v>0.2337303410836579</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.035714040555755</v>
+        <v>0.035108717834471</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2074492070059118</v>
+        <v>0.2093492070059118</v>
       </c>
       <c r="C61">
-        <v>-152.0319800987396</v>
+        <v>-159.7211203203241</v>
       </c>
       <c r="D61">
-        <v>176.9809199012604</v>
+        <v>174.924879679676</v>
       </c>
       <c r="E61">
-        <v>330.6429000000001</v>
+        <v>336.2760000000001</v>
       </c>
       <c r="F61">
-        <v>332.3529</v>
+        <v>337.986</v>
       </c>
       <c r="G61">
         <v>3.34</v>
@@ -6277,37 +6277,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M61">
-        <v>78.36881382000001</v>
+        <v>79.69709880000002</v>
       </c>
       <c r="N61">
-        <v>-75.61738524857144</v>
+        <v>-76.94567022857144</v>
       </c>
       <c r="O61">
-        <v>-18.90434631214286</v>
+        <v>-19.23641755714286</v>
       </c>
       <c r="P61">
-        <v>-56.71303893642857</v>
+        <v>-57.70925267142859</v>
       </c>
       <c r="Q61">
-        <v>-56.39303893642857</v>
+        <v>-57.38925267142859</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1696300140647648</v>
+        <v>0.172725764416384</v>
       </c>
       <c r="T61">
-        <v>1.197530877106018</v>
+        <v>1.227469149033668</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.008777179458617747</v>
+        <v>0.008630893134307451</v>
       </c>
       <c r="W61">
-        <v>0.2337303410836579</v>
+        <v>0.2337648353989303</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.035108717834471</v>
+        <v>0.03452357253722982</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2093492070059118</v>
+        <v>0.2112492070059118</v>
       </c>
       <c r="C62">
-        <v>-159.7211203203241</v>
+        <v>-167.3630378747019</v>
       </c>
       <c r="D62">
-        <v>174.924879679676</v>
+        <v>172.9160621252981</v>
       </c>
       <c r="E62">
-        <v>336.2760000000001</v>
+        <v>341.9091</v>
       </c>
       <c r="F62">
-        <v>337.986</v>
+        <v>343.6191</v>
       </c>
       <c r="G62">
         <v>3.34</v>
@@ -6359,37 +6359,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M62">
-        <v>79.69709880000002</v>
+        <v>81.02538378</v>
       </c>
       <c r="N62">
-        <v>-76.94567022857144</v>
+        <v>-78.27395520857142</v>
       </c>
       <c r="O62">
-        <v>-19.23641755714286</v>
+        <v>-19.56848880214286</v>
       </c>
       <c r="P62">
-        <v>-57.70925267142859</v>
+        <v>-58.70546640642857</v>
       </c>
       <c r="Q62">
-        <v>-57.38925267142859</v>
+        <v>-58.38546640642857</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.172725764416384</v>
+        <v>0.1759802711962912</v>
       </c>
       <c r="T62">
-        <v>1.227469149033668</v>
+        <v>1.258942716957609</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.008630893134307451</v>
+        <v>0.008489403082925364</v>
       </c>
       <c r="W62">
-        <v>0.2337648353989303</v>
+        <v>0.2337981987530462</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.03452357253722982</v>
+        <v>0.03395761233170147</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2112492070059118</v>
+        <v>0.2131492070059118</v>
       </c>
       <c r="C63">
-        <v>-167.3630378747019</v>
+        <v>-174.9593411901886</v>
       </c>
       <c r="D63">
-        <v>172.9160621252981</v>
+        <v>170.9528588098114</v>
       </c>
       <c r="E63">
-        <v>341.9091</v>
+        <v>347.5422</v>
       </c>
       <c r="F63">
-        <v>343.6191</v>
+        <v>349.2522</v>
       </c>
       <c r="G63">
         <v>3.34</v>
@@ -6441,37 +6441,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M63">
-        <v>81.02538378</v>
+        <v>82.35366876000001</v>
       </c>
       <c r="N63">
-        <v>-78.27395520857142</v>
+        <v>-79.60224018857143</v>
       </c>
       <c r="O63">
-        <v>-19.56848880214286</v>
+        <v>-19.90056004714286</v>
       </c>
       <c r="P63">
-        <v>-58.70546640642857</v>
+        <v>-59.70168014142857</v>
       </c>
       <c r="Q63">
-        <v>-58.38546640642857</v>
+        <v>-59.38168014142857</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1759802711962912</v>
+        <v>0.1794060678067199</v>
       </c>
       <c r="T63">
-        <v>1.258942716957609</v>
+        <v>1.292072788456493</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.008489403082925364</v>
+        <v>0.008352477226749148</v>
       </c>
       <c r="W63">
-        <v>0.2337981987530462</v>
+        <v>0.2338304858699326</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.03395761233170147</v>
+        <v>0.03340990890699669</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2131492070059118</v>
+        <v>0.2150492070059118</v>
       </c>
       <c r="C64">
-        <v>-174.9593411901886</v>
+        <v>-182.5115664699147</v>
       </c>
       <c r="D64">
-        <v>170.9528588098114</v>
+        <v>169.0337335300854</v>
       </c>
       <c r="E64">
-        <v>347.5422</v>
+        <v>353.1753</v>
       </c>
       <c r="F64">
-        <v>349.2522</v>
+        <v>354.8853</v>
       </c>
       <c r="G64">
         <v>3.34</v>
@@ -6523,37 +6523,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M64">
-        <v>82.35366876000001</v>
+        <v>83.68195374000001</v>
       </c>
       <c r="N64">
-        <v>-79.60224018857143</v>
+        <v>-80.93052516857144</v>
       </c>
       <c r="O64">
-        <v>-19.90056004714286</v>
+        <v>-20.23263129214286</v>
       </c>
       <c r="P64">
-        <v>-59.70168014142857</v>
+        <v>-60.69789387642858</v>
       </c>
       <c r="Q64">
-        <v>-59.38168014142857</v>
+        <v>-60.37789387642858</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1794060678067199</v>
+        <v>0.1830170426123069</v>
       </c>
       <c r="T64">
-        <v>1.292072788456493</v>
+        <v>1.326993674630993</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.008352477226749148</v>
+        <v>0.008219898223149955</v>
       </c>
       <c r="W64">
-        <v>0.2338304858699326</v>
+        <v>0.2338617479989812</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.03340990890699669</v>
+        <v>0.0328795928925999</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2150492070059118</v>
+        <v>0.2169492070059117</v>
       </c>
       <c r="C65">
-        <v>-182.5115664699147</v>
+        <v>-190.0211817008387</v>
       </c>
       <c r="D65">
-        <v>169.0337335300854</v>
+        <v>167.1572182991613</v>
       </c>
       <c r="E65">
-        <v>353.1753</v>
+        <v>358.8084000000001</v>
       </c>
       <c r="F65">
-        <v>354.8853</v>
+        <v>360.5184</v>
       </c>
       <c r="G65">
         <v>3.34</v>
@@ -6605,37 +6605,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M65">
-        <v>83.68195374000001</v>
+        <v>85.01023872000002</v>
       </c>
       <c r="N65">
-        <v>-80.93052516857144</v>
+        <v>-82.25881014857144</v>
       </c>
       <c r="O65">
-        <v>-20.23263129214286</v>
+        <v>-20.56470253714286</v>
       </c>
       <c r="P65">
-        <v>-60.69789387642858</v>
+        <v>-61.69410761142858</v>
       </c>
       <c r="Q65">
-        <v>-60.37789387642858</v>
+        <v>-61.37410761142858</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1830170426123069</v>
+        <v>0.1868286271293155</v>
       </c>
       <c r="T65">
-        <v>1.326993674630993</v>
+        <v>1.363854610037409</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.008219898223149955</v>
+        <v>0.008091462313413237</v>
       </c>
       <c r="W65">
-        <v>0.2338617479989812</v>
+        <v>0.2338920331864972</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.0328795928925999</v>
+        <v>0.03236584925365305</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2169492070059117</v>
+        <v>0.2188492070059118</v>
       </c>
       <c r="C66">
-        <v>-190.0211817008387</v>
+        <v>-197.4895903986565</v>
       </c>
       <c r="D66">
-        <v>167.1572182991613</v>
+        <v>165.3219096013436</v>
       </c>
       <c r="E66">
-        <v>358.8084000000001</v>
+        <v>364.4415000000001</v>
       </c>
       <c r="F66">
-        <v>360.5184</v>
+        <v>366.1515000000001</v>
       </c>
       <c r="G66">
         <v>3.34</v>
@@ -6687,37 +6687,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M66">
-        <v>85.01023872000002</v>
+        <v>86.33852370000001</v>
       </c>
       <c r="N66">
-        <v>-82.25881014857144</v>
+        <v>-83.58709512857143</v>
       </c>
       <c r="O66">
-        <v>-20.56470253714286</v>
+        <v>-20.89677378214286</v>
       </c>
       <c r="P66">
-        <v>-61.69410761142858</v>
+        <v>-62.69032134642858</v>
       </c>
       <c r="Q66">
-        <v>-61.37410761142858</v>
+        <v>-62.37032134642858</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1868286271293155</v>
+        <v>0.1908580164758674</v>
       </c>
       <c r="T66">
-        <v>1.363854610037409</v>
+        <v>1.402821884609907</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.008091462313413237</v>
+        <v>0.007966978277822265</v>
       </c>
       <c r="W66">
-        <v>0.2338920331864972</v>
+        <v>0.2339213865220895</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.03236584925365305</v>
+        <v>0.03186791311128911</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2188492070059118</v>
+        <v>0.2207492070059118</v>
       </c>
       <c r="C67">
-        <v>-197.4895903986565</v>
+        <v>-204.9181351086856</v>
       </c>
       <c r="D67">
-        <v>165.3219096013436</v>
+        <v>163.5264648913145</v>
       </c>
       <c r="E67">
-        <v>364.4415000000001</v>
+        <v>370.0746000000001</v>
       </c>
       <c r="F67">
-        <v>366.1515000000001</v>
+        <v>371.7846000000001</v>
       </c>
       <c r="G67">
         <v>3.34</v>
@@ -6769,37 +6769,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M67">
-        <v>86.33852370000001</v>
+        <v>87.66680868000002</v>
       </c>
       <c r="N67">
-        <v>-83.58709512857143</v>
+        <v>-84.91538010857144</v>
       </c>
       <c r="O67">
-        <v>-20.89677378214286</v>
+        <v>-21.22884502714286</v>
       </c>
       <c r="P67">
-        <v>-62.69032134642858</v>
+        <v>-63.68653508142858</v>
       </c>
       <c r="Q67">
-        <v>-62.37032134642858</v>
+        <v>-63.36653508142858</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1908580164758674</v>
+        <v>0.1951244287251576</v>
       </c>
       <c r="T67">
-        <v>1.402821884609907</v>
+        <v>1.444081351804316</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.007966978277822265</v>
+        <v>0.007846266485734048</v>
       </c>
       <c r="W67">
-        <v>0.2339213865220895</v>
+        <v>0.2339498503626639</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.03186791311128911</v>
+        <v>0.03138506594293622</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2207492070059118</v>
+        <v>0.2226492070059118</v>
       </c>
       <c r="C68">
-        <v>-204.9181351086856</v>
+        <v>-212.3081006810775</v>
       </c>
       <c r="D68">
-        <v>163.5264648913145</v>
+        <v>161.7695993189226</v>
       </c>
       <c r="E68">
-        <v>370.0746000000001</v>
+        <v>375.7077000000001</v>
       </c>
       <c r="F68">
-        <v>371.7846000000001</v>
+        <v>377.4177000000001</v>
       </c>
       <c r="G68">
         <v>3.34</v>
@@ -6851,37 +6851,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M68">
-        <v>87.66680868000002</v>
+        <v>88.99509366000002</v>
       </c>
       <c r="N68">
-        <v>-84.91538010857144</v>
+        <v>-86.24366508857145</v>
       </c>
       <c r="O68">
-        <v>-21.22884502714286</v>
+        <v>-21.56091627214286</v>
       </c>
       <c r="P68">
-        <v>-63.68653508142858</v>
+        <v>-64.68274881642859</v>
       </c>
       <c r="Q68">
-        <v>-63.36653508142858</v>
+        <v>-64.36274881642859</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1951244287251576</v>
+        <v>0.1996494114137988</v>
       </c>
       <c r="T68">
-        <v>1.444081351804316</v>
+        <v>1.487841392768083</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.007846266485734048</v>
+        <v>0.007729158030723091</v>
       </c>
       <c r="W68">
-        <v>0.2339498503626639</v>
+        <v>0.2339774645363555</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.03138506594293622</v>
+        <v>0.03091663212289242</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2226492070059118</v>
+        <v>0.2245492070059118</v>
       </c>
       <c r="C69">
-        <v>-212.3081006810775</v>
+        <v>-219.6607173371474</v>
       </c>
       <c r="D69">
-        <v>161.7695993189226</v>
+        <v>160.0500826628526</v>
       </c>
       <c r="E69">
-        <v>375.7077000000001</v>
+        <v>381.3408000000001</v>
       </c>
       <c r="F69">
-        <v>377.4177000000001</v>
+        <v>383.0508000000001</v>
       </c>
       <c r="G69">
         <v>3.34</v>
@@ -6933,37 +6933,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M69">
-        <v>88.99509366000002</v>
+        <v>90.32337864000003</v>
       </c>
       <c r="N69">
-        <v>-86.24366508857145</v>
+        <v>-87.57195006857145</v>
       </c>
       <c r="O69">
-        <v>-21.56091627214286</v>
+        <v>-21.89298751714286</v>
       </c>
       <c r="P69">
-        <v>-64.68274881642859</v>
+        <v>-65.67896255142858</v>
       </c>
       <c r="Q69">
-        <v>-64.36274881642859</v>
+        <v>-65.35896255142859</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1996494114137988</v>
+        <v>0.20445720552048</v>
       </c>
       <c r="T69">
-        <v>1.487841392768083</v>
+        <v>1.534336436292086</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.007729158030723091</v>
+        <v>0.007615493942035987</v>
       </c>
       <c r="W69">
-        <v>0.2339774645363555</v>
+        <v>0.2340042665284679</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.03091663212289242</v>
+        <v>0.03046197576814402</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2245492070059118</v>
+        <v>0.2264492070059118</v>
       </c>
       <c r="C70">
-        <v>-219.6607173371474</v>
+        <v>-226.9771635422015</v>
       </c>
       <c r="D70">
-        <v>160.0500826628526</v>
+        <v>158.3667364577986</v>
       </c>
       <c r="E70">
-        <v>381.3408000000001</v>
+        <v>386.9739000000001</v>
       </c>
       <c r="F70">
-        <v>383.0508000000001</v>
+        <v>388.6839000000001</v>
       </c>
       <c r="G70">
         <v>3.34</v>
@@ -7015,37 +7015,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M70">
-        <v>90.32337864000003</v>
+        <v>91.65166362000002</v>
       </c>
       <c r="N70">
-        <v>-87.57195006857145</v>
+        <v>-88.90023504857145</v>
       </c>
       <c r="O70">
-        <v>-21.89298751714286</v>
+        <v>-22.22505876214286</v>
       </c>
       <c r="P70">
-        <v>-65.67896255142858</v>
+        <v>-66.67517628642858</v>
       </c>
       <c r="Q70">
-        <v>-65.35896255142859</v>
+        <v>-66.35517628642859</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.20445720552048</v>
+        <v>0.2095751798921084</v>
       </c>
       <c r="T70">
-        <v>1.534336436292086</v>
+        <v>1.583831160043444</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.007615493942035987</v>
+        <v>0.007505124464615175</v>
       </c>
       <c r="W70">
-        <v>0.2340042665284679</v>
+        <v>0.2340302916512438</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.03046197576814402</v>
+        <v>0.03002049785846073</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2264492070059118</v>
+        <v>0.2283492070059118</v>
       </c>
       <c r="C71">
-        <v>-226.9771635422015</v>
+        <v>-234.2585686989588</v>
       </c>
       <c r="D71">
-        <v>158.3667364577986</v>
+        <v>156.7184313010413</v>
       </c>
       <c r="E71">
-        <v>386.9739000000001</v>
+        <v>392.6070000000001</v>
       </c>
       <c r="F71">
-        <v>388.6839000000001</v>
+        <v>394.3170000000001</v>
       </c>
       <c r="G71">
         <v>3.34</v>
@@ -7097,37 +7097,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M71">
-        <v>91.65166362000002</v>
+        <v>92.97994860000001</v>
       </c>
       <c r="N71">
-        <v>-88.90023504857145</v>
+        <v>-90.22852002857144</v>
       </c>
       <c r="O71">
-        <v>-22.22505876214286</v>
+        <v>-22.55713000714286</v>
       </c>
       <c r="P71">
-        <v>-66.67517628642858</v>
+        <v>-67.67139002142858</v>
       </c>
       <c r="Q71">
-        <v>-66.35517628642859</v>
+        <v>-67.35139002142859</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2095751798921084</v>
+        <v>0.2150343525551786</v>
       </c>
       <c r="T71">
-        <v>1.583831160043444</v>
+        <v>1.636625532044891</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.007505124464615175</v>
+        <v>0.00739790840083496</v>
       </c>
       <c r="W71">
-        <v>0.2340302916512438</v>
+        <v>0.2340555731990831</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.03002049785846073</v>
+        <v>0.02959163360333994</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2283492070059118</v>
+        <v>0.2302492070059118</v>
       </c>
       <c r="C72">
-        <v>-234.2585686989588</v>
+        <v>-241.5060156745055</v>
       </c>
       <c r="D72">
-        <v>156.7184313010413</v>
+        <v>155.1040843254946</v>
       </c>
       <c r="E72">
-        <v>392.6070000000001</v>
+        <v>398.2401000000001</v>
       </c>
       <c r="F72">
-        <v>394.3170000000001</v>
+        <v>399.9501000000001</v>
       </c>
       <c r="G72">
         <v>3.34</v>
@@ -7179,37 +7179,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M72">
-        <v>92.97994860000001</v>
+        <v>94.30823358000002</v>
       </c>
       <c r="N72">
-        <v>-90.22852002857144</v>
+        <v>-91.55680500857144</v>
       </c>
       <c r="O72">
-        <v>-22.55713000714286</v>
+        <v>-22.88920125214286</v>
       </c>
       <c r="P72">
-        <v>-67.67139002142858</v>
+        <v>-68.66760375642858</v>
       </c>
       <c r="Q72">
-        <v>-67.35139002142859</v>
+        <v>-68.34760375642858</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2150343525551786</v>
+        <v>0.2208700198846676</v>
       </c>
       <c r="T72">
-        <v>1.636625532044891</v>
+        <v>1.693060895218854</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.00739790840083496</v>
+        <v>0.007293712507865453</v>
       </c>
       <c r="W72">
-        <v>0.2340555731990831</v>
+        <v>0.2340801425906453</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.02959163360333994</v>
+        <v>0.02917485003146181</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2302492070059118</v>
+        <v>0.2321492070059118</v>
       </c>
       <c r="C73">
-        <v>-241.5060156745054</v>
+        <v>-248.72054317266</v>
       </c>
       <c r="D73">
-        <v>155.1040843254946</v>
+        <v>153.52265682734</v>
       </c>
       <c r="E73">
-        <v>398.2401</v>
+        <v>403.8732000000001</v>
       </c>
       <c r="F73">
-        <v>399.9501</v>
+        <v>405.5832</v>
       </c>
       <c r="G73">
         <v>3.34</v>
@@ -7261,37 +7261,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M73">
-        <v>94.30823358000001</v>
+        <v>95.63651856000001</v>
       </c>
       <c r="N73">
-        <v>-91.55680500857143</v>
+        <v>-92.88508998857144</v>
       </c>
       <c r="O73">
-        <v>-22.88920125214286</v>
+        <v>-23.22127249714286</v>
       </c>
       <c r="P73">
-        <v>-68.66760375642858</v>
+        <v>-69.66381749142857</v>
       </c>
       <c r="Q73">
-        <v>-68.34760375642858</v>
+        <v>-69.34381749142858</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2208700198846675</v>
+        <v>0.2271225205948342</v>
       </c>
       <c r="T73">
-        <v>1.693060895218853</v>
+        <v>1.753527355762383</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.007293712507865454</v>
+        <v>0.007192410945256211</v>
       </c>
       <c r="W73">
-        <v>0.2340801425906453</v>
+        <v>0.2341040294991086</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.02917485003146192</v>
+        <v>0.02876964378102487</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2321492070059118</v>
+        <v>0.2340492070059118</v>
       </c>
       <c r="C74">
-        <v>-248.72054317266</v>
+        <v>-255.9031479626737</v>
       </c>
       <c r="D74">
-        <v>153.52265682734</v>
+        <v>151.9731520373264</v>
       </c>
       <c r="E74">
-        <v>403.8732000000001</v>
+        <v>409.5063000000001</v>
       </c>
       <c r="F74">
-        <v>405.5832</v>
+        <v>411.2163</v>
       </c>
       <c r="G74">
         <v>3.34</v>
@@ -7343,37 +7343,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M74">
-        <v>95.63651856000001</v>
+        <v>96.96480354000002</v>
       </c>
       <c r="N74">
-        <v>-92.88508998857144</v>
+        <v>-94.21337496857144</v>
       </c>
       <c r="O74">
-        <v>-23.22127249714286</v>
+        <v>-23.55334374214286</v>
       </c>
       <c r="P74">
-        <v>-69.66381749142857</v>
+        <v>-70.66003122642859</v>
       </c>
       <c r="Q74">
-        <v>-69.34381749142858</v>
+        <v>-70.34003122642859</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2271225205948342</v>
+        <v>0.233838169505754</v>
       </c>
       <c r="T74">
-        <v>1.753527355762383</v>
+        <v>1.818472813383212</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.007192410945256211</v>
+        <v>0.007093884767923934</v>
       </c>
       <c r="W74">
-        <v>0.2341040294991086</v>
+        <v>0.2341272619717235</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.02876964378102487</v>
+        <v>0.02837553907169577</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2340492070059118</v>
+        <v>0.2359492070059118</v>
       </c>
       <c r="C75">
-        <v>-255.9031479626737</v>
+        <v>-263.0547869743139</v>
       </c>
       <c r="D75">
-        <v>151.9731520373264</v>
+        <v>150.4546130256862</v>
       </c>
       <c r="E75">
-        <v>409.5063000000001</v>
+        <v>415.1394000000001</v>
       </c>
       <c r="F75">
-        <v>411.2163</v>
+        <v>416.8494000000001</v>
       </c>
       <c r="G75">
         <v>3.34</v>
@@ -7425,37 +7425,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M75">
-        <v>96.96480354000002</v>
+        <v>98.29308852000001</v>
       </c>
       <c r="N75">
-        <v>-94.21337496857144</v>
+        <v>-95.54165994857144</v>
       </c>
       <c r="O75">
-        <v>-23.55334374214286</v>
+        <v>-23.88541498714286</v>
       </c>
       <c r="P75">
-        <v>-70.66003122642859</v>
+        <v>-71.65624496142857</v>
       </c>
       <c r="Q75">
-        <v>-70.34003122642859</v>
+        <v>-71.33624496142858</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.233838169505754</v>
+        <v>0.2410704067944368</v>
       </c>
       <c r="T75">
-        <v>1.818472813383212</v>
+        <v>1.888414075436413</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.007093884767923934</v>
+        <v>0.006998021460249286</v>
       </c>
       <c r="W75">
-        <v>0.2341272619717235</v>
+        <v>0.2341498665396732</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.02837553907169577</v>
+        <v>0.02799208584099722</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2359492070059118</v>
+        <v>0.2378492070059118</v>
       </c>
       <c r="C76">
-        <v>-263.0547869743139</v>
+        <v>-270.1763792685831</v>
       </c>
       <c r="D76">
-        <v>150.4546130256862</v>
+        <v>148.9661207314169</v>
       </c>
       <c r="E76">
-        <v>415.1394000000001</v>
+        <v>420.7725000000001</v>
       </c>
       <c r="F76">
-        <v>416.8494000000001</v>
+        <v>422.4825000000001</v>
       </c>
       <c r="G76">
         <v>3.34</v>
@@ -7507,37 +7507,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M76">
-        <v>98.29308852000001</v>
+        <v>99.62137350000002</v>
       </c>
       <c r="N76">
-        <v>-95.54165994857144</v>
+        <v>-96.86994492857144</v>
       </c>
       <c r="O76">
-        <v>-23.88541498714286</v>
+        <v>-24.21748623214286</v>
       </c>
       <c r="P76">
-        <v>-71.65624496142857</v>
+        <v>-72.65245869642858</v>
       </c>
       <c r="Q76">
-        <v>-71.33624496142858</v>
+        <v>-72.33245869642859</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2410704067944368</v>
+        <v>0.2488812230662143</v>
       </c>
       <c r="T76">
-        <v>1.888414075436413</v>
+        <v>1.96395063845387</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.006998021460249286</v>
+        <v>0.006904714507445962</v>
       </c>
       <c r="W76">
-        <v>0.2341498665396732</v>
+        <v>0.2341718683191442</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.02799208584099722</v>
+        <v>0.02761885802978392</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2378492070059118</v>
+        <v>0.2397492070059118</v>
       </c>
       <c r="C77">
-        <v>-270.1763792685831</v>
+        <v>-277.268807892603</v>
       </c>
       <c r="D77">
-        <v>148.9661207314169</v>
+        <v>147.506792107397</v>
       </c>
       <c r="E77">
-        <v>420.7725000000001</v>
+        <v>426.4056</v>
       </c>
       <c r="F77">
-        <v>422.4825000000001</v>
+        <v>428.1156</v>
       </c>
       <c r="G77">
         <v>3.34</v>
@@ -7589,37 +7589,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M77">
-        <v>99.62137350000002</v>
+        <v>100.94965848</v>
       </c>
       <c r="N77">
-        <v>-96.86994492857144</v>
+        <v>-98.19822990857143</v>
       </c>
       <c r="O77">
-        <v>-24.21748623214286</v>
+        <v>-24.54955747714286</v>
       </c>
       <c r="P77">
-        <v>-72.65245869642858</v>
+        <v>-73.64867243142858</v>
       </c>
       <c r="Q77">
-        <v>-72.33245869642859</v>
+        <v>-73.32867243142859</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2488812230662143</v>
+        <v>0.2573429406939733</v>
       </c>
       <c r="T77">
-        <v>1.96395063845387</v>
+        <v>2.045781915056115</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.006904714507445962</v>
+        <v>0.006813863000769042</v>
       </c>
       <c r="W77">
-        <v>0.2341718683191442</v>
+        <v>0.2341932911044187</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.02761885802978392</v>
+        <v>0.02725545200307622</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2397492070059118</v>
+        <v>0.2416492070059117</v>
       </c>
       <c r="C78">
-        <v>-277.268807892603</v>
+        <v>-284.3329216265294</v>
       </c>
       <c r="D78">
-        <v>147.506792107397</v>
+        <v>146.0757783734706</v>
       </c>
       <c r="E78">
-        <v>426.4056</v>
+        <v>432.0387000000001</v>
       </c>
       <c r="F78">
-        <v>428.1156</v>
+        <v>433.7487</v>
       </c>
       <c r="G78">
         <v>3.34</v>
@@ -7671,37 +7671,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M78">
-        <v>100.94965848</v>
+        <v>102.27794346</v>
       </c>
       <c r="N78">
-        <v>-98.19822990857143</v>
+        <v>-99.52651488857144</v>
       </c>
       <c r="O78">
-        <v>-24.54955747714286</v>
+        <v>-24.88162872214286</v>
       </c>
       <c r="P78">
-        <v>-73.64867243142858</v>
+        <v>-74.64488616642858</v>
       </c>
       <c r="Q78">
-        <v>-73.32867243142859</v>
+        <v>-74.32488616642858</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2573429406939733</v>
+        <v>0.2665404598545807</v>
       </c>
       <c r="T78">
-        <v>2.045781915056115</v>
+        <v>2.134728954841162</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.006813863000769042</v>
+        <v>0.006725371273486326</v>
       </c>
       <c r="W78">
-        <v>0.2341932911044187</v>
+        <v>0.2342141574537119</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.02725545200307622</v>
+        <v>0.02690148509394541</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2416492070059117</v>
+        <v>0.2435492070059118</v>
       </c>
       <c r="C79">
-        <v>-284.3329216265294</v>
+        <v>-291.3695366297592</v>
       </c>
       <c r="D79">
-        <v>146.0757783734706</v>
+        <v>144.6722633702409</v>
       </c>
       <c r="E79">
-        <v>432.0387000000001</v>
+        <v>437.6718000000001</v>
       </c>
       <c r="F79">
-        <v>433.7487</v>
+        <v>439.3818000000001</v>
       </c>
       <c r="G79">
         <v>3.34</v>
@@ -7753,37 +7753,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M79">
-        <v>102.27794346</v>
+        <v>103.60622844</v>
       </c>
       <c r="N79">
-        <v>-99.52651488857144</v>
+        <v>-100.8547998685714</v>
       </c>
       <c r="O79">
-        <v>-24.88162872214286</v>
+        <v>-25.21369996714286</v>
       </c>
       <c r="P79">
-        <v>-74.64488616642858</v>
+        <v>-75.64109990142859</v>
       </c>
       <c r="Q79">
-        <v>-74.32488616642858</v>
+        <v>-75.3210999014286</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2665404598545807</v>
+        <v>0.2765741171206981</v>
       </c>
       <c r="T79">
-        <v>2.134728954841162</v>
+        <v>2.231762089152125</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.006725371273486326</v>
+        <v>0.006639148564851886</v>
       </c>
       <c r="W79">
-        <v>0.2342141574537119</v>
+        <v>0.2342344887684079</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02690148509394541</v>
+        <v>0.0265565942594076</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2435492070059118</v>
+        <v>0.2454492070059117</v>
       </c>
       <c r="C80">
-        <v>-291.3695366297592</v>
+        <v>-298.3794379931392</v>
       </c>
       <c r="D80">
-        <v>144.6722633702409</v>
+        <v>143.2954620068609</v>
       </c>
       <c r="E80">
-        <v>437.6718000000001</v>
+        <v>443.3049000000001</v>
       </c>
       <c r="F80">
-        <v>439.3818000000001</v>
+        <v>445.0149000000001</v>
       </c>
       <c r="G80">
         <v>3.34</v>
@@ -7835,37 +7835,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M80">
-        <v>103.60622844</v>
+        <v>104.93451342</v>
       </c>
       <c r="N80">
-        <v>-100.8547998685714</v>
+        <v>-102.1830848485714</v>
       </c>
       <c r="O80">
-        <v>-25.21369996714286</v>
+        <v>-25.54577121214286</v>
       </c>
       <c r="P80">
-        <v>-75.64109990142859</v>
+        <v>-76.63731363642859</v>
       </c>
       <c r="Q80">
-        <v>-75.3210999014286</v>
+        <v>-76.31731363642859</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2765741171206981</v>
+        <v>0.2875633607931123</v>
       </c>
       <c r="T80">
-        <v>2.231762089152125</v>
+        <v>2.338036474349845</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.006639148564851886</v>
+        <v>0.006555108709600597</v>
       </c>
       <c r="W80">
-        <v>0.2342344887684079</v>
+        <v>0.2342543053662762</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0265565942594076</v>
+        <v>0.02622043483840242</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2454492070059117</v>
+        <v>0.2473492070059118</v>
       </c>
       <c r="C81">
-        <v>-298.3794379931392</v>
+        <v>-305.3633812033784</v>
       </c>
       <c r="D81">
-        <v>143.2954620068609</v>
+        <v>141.9446187966217</v>
       </c>
       <c r="E81">
-        <v>443.3049000000001</v>
+        <v>448.9380000000001</v>
       </c>
       <c r="F81">
-        <v>445.0149000000001</v>
+        <v>450.6480000000001</v>
       </c>
       <c r="G81">
         <v>3.34</v>
@@ -7917,37 +7917,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M81">
-        <v>104.93451342</v>
+        <v>106.2627984</v>
       </c>
       <c r="N81">
-        <v>-102.1830848485714</v>
+        <v>-103.5113698285714</v>
       </c>
       <c r="O81">
-        <v>-25.54577121214286</v>
+        <v>-25.87784245714286</v>
       </c>
       <c r="P81">
-        <v>-76.63731363642859</v>
+        <v>-77.63352737142858</v>
       </c>
       <c r="Q81">
-        <v>-76.31731363642859</v>
+        <v>-77.31352737142859</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2875633607931123</v>
+        <v>0.2996515288327679</v>
       </c>
       <c r="T81">
-        <v>2.338036474349845</v>
+        <v>2.454938298067337</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.006555108709600597</v>
+        <v>0.006473169850730589</v>
       </c>
       <c r="W81">
-        <v>0.2342543053662762</v>
+        <v>0.2342736265491978</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.02622043483840242</v>
+        <v>0.02589267940292239</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2473492070059118</v>
+        <v>0.2492492070059118</v>
       </c>
       <c r="C82">
-        <v>-305.3633812033784</v>
+        <v>-312.3220935254051</v>
       </c>
       <c r="D82">
-        <v>141.9446187966217</v>
+        <v>140.619006474595</v>
       </c>
       <c r="E82">
-        <v>448.9380000000001</v>
+        <v>454.5711000000001</v>
       </c>
       <c r="F82">
-        <v>450.6480000000001</v>
+        <v>456.2811000000001</v>
       </c>
       <c r="G82">
         <v>3.34</v>
@@ -7999,37 +7999,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M82">
-        <v>106.2627984</v>
+        <v>107.59108338</v>
       </c>
       <c r="N82">
-        <v>-103.5113698285714</v>
+        <v>-104.8396548085715</v>
       </c>
       <c r="O82">
-        <v>-25.87784245714286</v>
+        <v>-26.20991370214286</v>
       </c>
       <c r="P82">
-        <v>-77.63352737142858</v>
+        <v>-78.62974110642858</v>
       </c>
       <c r="Q82">
-        <v>-77.31352737142859</v>
+        <v>-78.30974110642859</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2996515288327679</v>
+        <v>0.31301213561344</v>
       </c>
       <c r="T82">
-        <v>2.454938298067337</v>
+        <v>2.584145576912987</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.006473169850730589</v>
+        <v>0.006393254173561075</v>
       </c>
       <c r="W82">
-        <v>0.2342736265491978</v>
+        <v>0.2342924706658743</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02589267940292239</v>
+        <v>0.02557301669424439</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2492492070059118</v>
+        <v>0.2511492070059118</v>
       </c>
       <c r="C83">
-        <v>-312.3220935254051</v>
+        <v>-319.2562753079806</v>
       </c>
       <c r="D83">
-        <v>140.619006474595</v>
+        <v>139.3179246920195</v>
       </c>
       <c r="E83">
-        <v>454.5711000000001</v>
+        <v>460.2042000000001</v>
       </c>
       <c r="F83">
-        <v>456.2811000000001</v>
+        <v>461.9142000000001</v>
       </c>
       <c r="G83">
         <v>3.34</v>
@@ -8081,37 +8081,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M83">
-        <v>107.59108338</v>
+        <v>108.91936836</v>
       </c>
       <c r="N83">
-        <v>-104.8396548085715</v>
+        <v>-106.1679397885715</v>
       </c>
       <c r="O83">
-        <v>-26.20991370214286</v>
+        <v>-26.54198494714286</v>
       </c>
       <c r="P83">
-        <v>-78.62974110642858</v>
+        <v>-79.62595484142859</v>
       </c>
       <c r="Q83">
-        <v>-78.30974110642859</v>
+        <v>-79.3059548414286</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.31301213561344</v>
+        <v>0.3278572542586311</v>
       </c>
       <c r="T83">
-        <v>2.584145576912987</v>
+        <v>2.72770922007482</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.006393254173561075</v>
+        <v>0.006315287659249355</v>
       </c>
       <c r="W83">
-        <v>0.2342924706658743</v>
+        <v>0.234310855169949</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.02557301669424439</v>
+        <v>0.02526115063699741</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2511492070059118</v>
+        <v>0.2530492070059118</v>
       </c>
       <c r="C84">
-        <v>-319.2562753079806</v>
+        <v>-326.1666012174977</v>
       </c>
       <c r="D84">
-        <v>139.3179246920195</v>
+        <v>138.0406987825023</v>
       </c>
       <c r="E84">
-        <v>460.2042000000001</v>
+        <v>465.8373000000001</v>
       </c>
       <c r="F84">
-        <v>461.9142000000001</v>
+        <v>467.5473000000001</v>
       </c>
       <c r="G84">
         <v>3.34</v>
@@ -8163,37 +8163,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M84">
-        <v>108.91936836</v>
+        <v>110.24765334</v>
       </c>
       <c r="N84">
-        <v>-106.1679397885715</v>
+        <v>-107.4962247685714</v>
       </c>
       <c r="O84">
-        <v>-26.54198494714286</v>
+        <v>-26.87405619214286</v>
       </c>
       <c r="P84">
-        <v>-79.62595484142859</v>
+        <v>-80.62216857642858</v>
       </c>
       <c r="Q84">
-        <v>-79.3059548414286</v>
+        <v>-80.30216857642858</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3278572542586311</v>
+        <v>0.3444488574503153</v>
       </c>
       <c r="T84">
-        <v>2.72770922007482</v>
+        <v>2.888162703608633</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.006315287659249355</v>
+        <v>0.00623919985612587</v>
       </c>
       <c r="W84">
-        <v>0.234310855169949</v>
+        <v>0.2343287966739255</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02526115063699741</v>
+        <v>0.02495679942450357</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2530492070059118</v>
+        <v>0.2549492070059118</v>
       </c>
       <c r="C85">
-        <v>-326.1666012174977</v>
+        <v>-333.0537214045279</v>
       </c>
       <c r="D85">
-        <v>138.0406987825023</v>
+        <v>136.7866785954722</v>
       </c>
       <c r="E85">
-        <v>465.8373000000001</v>
+        <v>471.4704000000001</v>
       </c>
       <c r="F85">
-        <v>467.5473000000001</v>
+        <v>473.1804000000001</v>
       </c>
       <c r="G85">
         <v>3.34</v>
@@ -8245,37 +8245,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M85">
-        <v>110.24765334</v>
+        <v>111.57593832</v>
       </c>
       <c r="N85">
-        <v>-107.4962247685714</v>
+        <v>-108.8245097485714</v>
       </c>
       <c r="O85">
-        <v>-26.87405619214286</v>
+        <v>-27.20612743714286</v>
       </c>
       <c r="P85">
-        <v>-80.62216857642858</v>
+        <v>-81.61838231142858</v>
       </c>
       <c r="Q85">
-        <v>-80.30216857642858</v>
+        <v>-81.29838231142858</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3444488574503153</v>
+        <v>0.3631144110409601</v>
       </c>
       <c r="T85">
-        <v>2.888162703608633</v>
+        <v>3.068672872584173</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.00623919985612587</v>
+        <v>0.006164923667362466</v>
       </c>
       <c r="W85">
-        <v>0.2343287966739255</v>
+        <v>0.2343463109992359</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02495679942450357</v>
+        <v>0.02465969466944995</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2549492070059118</v>
+        <v>0.2568492070059118</v>
       </c>
       <c r="C86">
-        <v>-333.0537214045278</v>
+        <v>-339.9182626073565</v>
       </c>
       <c r="D86">
-        <v>136.7866785954723</v>
+        <v>135.5552373926436</v>
       </c>
       <c r="E86">
-        <v>471.4704</v>
+        <v>477.1035000000001</v>
       </c>
       <c r="F86">
-        <v>473.1804</v>
+        <v>478.8135</v>
       </c>
       <c r="G86">
         <v>3.34</v>
@@ -8327,37 +8327,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M86">
-        <v>111.57593832</v>
+        <v>112.9042233</v>
       </c>
       <c r="N86">
-        <v>-108.8245097485714</v>
+        <v>-110.1527947285714</v>
       </c>
       <c r="O86">
-        <v>-27.20612743714286</v>
+        <v>-27.53819868214286</v>
       </c>
       <c r="P86">
-        <v>-81.61838231142858</v>
+        <v>-82.61459604642857</v>
       </c>
       <c r="Q86">
-        <v>-81.29838231142858</v>
+        <v>-82.29459604642858</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3631144110409598</v>
+        <v>0.3842687051103572</v>
       </c>
       <c r="T86">
-        <v>3.068672872584171</v>
+        <v>3.273251064089782</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.006164923667362467</v>
+        <v>0.006092395153628791</v>
       </c>
       <c r="W86">
-        <v>0.2343463109992359</v>
+        <v>0.2343634132227743</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02465969466944995</v>
+        <v>0.02436958061451522</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2568492070059118</v>
+        <v>0.2587492070059118</v>
       </c>
       <c r="C87">
-        <v>-339.9182626073565</v>
+        <v>-346.7608291964425</v>
       </c>
       <c r="D87">
-        <v>135.5552373926436</v>
+        <v>134.3457708035575</v>
       </c>
       <c r="E87">
-        <v>477.1035000000001</v>
+        <v>482.7366000000001</v>
       </c>
       <c r="F87">
-        <v>478.8135</v>
+        <v>484.4466</v>
       </c>
       <c r="G87">
         <v>3.34</v>
@@ -8409,37 +8409,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M87">
-        <v>112.9042233</v>
+        <v>114.23250828</v>
       </c>
       <c r="N87">
-        <v>-110.1527947285714</v>
+        <v>-111.4810797085714</v>
       </c>
       <c r="O87">
-        <v>-27.53819868214286</v>
+        <v>-27.87026992714286</v>
       </c>
       <c r="P87">
-        <v>-82.61459604642857</v>
+        <v>-83.61080978142859</v>
       </c>
       <c r="Q87">
-        <v>-82.29459604642858</v>
+        <v>-83.29080978142859</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3842687051103572</v>
+        <v>0.4084450411896684</v>
       </c>
       <c r="T87">
-        <v>3.273251064089782</v>
+        <v>3.507054711524767</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.006092395153628791</v>
+        <v>0.006021553349516828</v>
       </c>
       <c r="W87">
-        <v>0.2343634132227743</v>
+        <v>0.2343801177201839</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02436958061451522</v>
+        <v>0.02408621339806738</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2587492070059118</v>
+        <v>0.2606492070059118</v>
       </c>
       <c r="C88">
-        <v>-346.7608291964425</v>
+        <v>-353.5820041634576</v>
       </c>
       <c r="D88">
-        <v>134.3457708035575</v>
+        <v>133.1576958365424</v>
       </c>
       <c r="E88">
-        <v>482.7366000000001</v>
+        <v>488.3697000000001</v>
       </c>
       <c r="F88">
-        <v>484.4466</v>
+        <v>490.0797000000001</v>
       </c>
       <c r="G88">
         <v>3.34</v>
@@ -8491,37 +8491,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M88">
-        <v>114.23250828</v>
+        <v>115.56079326</v>
       </c>
       <c r="N88">
-        <v>-111.4810797085714</v>
+        <v>-112.8093646885714</v>
       </c>
       <c r="O88">
-        <v>-27.87026992714286</v>
+        <v>-28.20234117214286</v>
       </c>
       <c r="P88">
-        <v>-83.61080978142859</v>
+        <v>-84.60702351642858</v>
       </c>
       <c r="Q88">
-        <v>-83.29080978142859</v>
+        <v>-84.28702351642859</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4084450411896684</v>
+        <v>0.4363408135888737</v>
       </c>
       <c r="T88">
-        <v>3.507054711524767</v>
+        <v>3.776828150872826</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.006021553349516828</v>
+        <v>0.005952340092625829</v>
       </c>
       <c r="W88">
-        <v>0.2343801177201839</v>
+        <v>0.2343964382061589</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02408621339806738</v>
+        <v>0.02380936037050341</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2606492070059118</v>
+        <v>0.2625492070059118</v>
       </c>
       <c r="C89">
-        <v>-353.5820041634576</v>
+        <v>-360.3823500583067</v>
       </c>
       <c r="D89">
-        <v>133.1576958365424</v>
+        <v>131.9904499416934</v>
       </c>
       <c r="E89">
-        <v>488.3697000000001</v>
+        <v>494.0028000000001</v>
       </c>
       <c r="F89">
-        <v>490.0797000000001</v>
+        <v>495.7128000000001</v>
       </c>
       <c r="G89">
         <v>3.34</v>
@@ -8573,37 +8573,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M89">
-        <v>115.56079326</v>
+        <v>116.88907824</v>
       </c>
       <c r="N89">
-        <v>-112.8093646885714</v>
+        <v>-114.1376496685714</v>
       </c>
       <c r="O89">
-        <v>-28.20234117214286</v>
+        <v>-28.53441241714286</v>
       </c>
       <c r="P89">
-        <v>-84.60702351642858</v>
+        <v>-85.60323725142858</v>
       </c>
       <c r="Q89">
-        <v>-84.28702351642859</v>
+        <v>-85.28323725142859</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4363408135888737</v>
+        <v>0.4688858813879466</v>
       </c>
       <c r="T89">
-        <v>3.776828150872826</v>
+        <v>4.091563830112229</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.005952340092625829</v>
+        <v>0.005884699864300536</v>
       </c>
       <c r="W89">
-        <v>0.2343964382061589</v>
+        <v>0.2344123877719979</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02380936037050341</v>
+        <v>0.02353879945720216</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2625492070059118</v>
+        <v>0.2644492070059118</v>
       </c>
       <c r="C90">
-        <v>-360.3823500583067</v>
+        <v>-367.162409877294</v>
       </c>
       <c r="D90">
-        <v>131.9904499416934</v>
+        <v>130.8434901227061</v>
       </c>
       <c r="E90">
-        <v>494.0028000000001</v>
+        <v>499.6359000000001</v>
       </c>
       <c r="F90">
-        <v>495.7128000000001</v>
+        <v>501.3459000000001</v>
       </c>
       <c r="G90">
         <v>3.34</v>
@@ -8655,37 +8655,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M90">
-        <v>116.88907824</v>
+        <v>118.21736322</v>
       </c>
       <c r="N90">
-        <v>-114.1376496685714</v>
+        <v>-115.4659346485714</v>
       </c>
       <c r="O90">
-        <v>-28.53441241714286</v>
+        <v>-28.86648366214286</v>
       </c>
       <c r="P90">
-        <v>-85.60323725142858</v>
+        <v>-86.59945098642859</v>
       </c>
       <c r="Q90">
-        <v>-85.28323725142859</v>
+        <v>-86.2794509864286</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4688858813879466</v>
+        <v>0.5073482342413962</v>
       </c>
       <c r="T90">
-        <v>4.091563830112229</v>
+        <v>4.463524178304249</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.005884699864300536</v>
+        <v>0.005818579641106147</v>
       </c>
       <c r="W90">
-        <v>0.2344123877719979</v>
+        <v>0.2344279789206272</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02353879945720216</v>
+        <v>0.02327431856442463</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2644492070059118</v>
+        <v>0.2663492070059117</v>
       </c>
       <c r="C91">
-        <v>-367.162409877294</v>
+        <v>-373.9227079053805</v>
       </c>
       <c r="D91">
-        <v>130.8434901227061</v>
+        <v>129.7162920946195</v>
       </c>
       <c r="E91">
-        <v>499.6359000000001</v>
+        <v>505.2690000000001</v>
       </c>
       <c r="F91">
-        <v>501.3459000000001</v>
+        <v>506.979</v>
       </c>
       <c r="G91">
         <v>3.34</v>
@@ -8737,37 +8737,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M91">
-        <v>118.21736322</v>
+        <v>119.5456482</v>
       </c>
       <c r="N91">
-        <v>-115.4659346485714</v>
+        <v>-116.7942196285714</v>
       </c>
       <c r="O91">
-        <v>-28.86648366214286</v>
+        <v>-29.19855490714286</v>
       </c>
       <c r="P91">
-        <v>-86.59945098642859</v>
+        <v>-87.59566472142858</v>
       </c>
       <c r="Q91">
-        <v>-86.2794509864286</v>
+        <v>-87.27566472142858</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5073482342413962</v>
+        <v>0.5535030576655358</v>
       </c>
       <c r="T91">
-        <v>4.463524178304249</v>
+        <v>4.909876596134675</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.005818579641106147</v>
+        <v>0.005753928756204969</v>
       </c>
       <c r="W91">
-        <v>0.2344279789206272</v>
+        <v>0.2344432235992869</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02327431856442463</v>
+        <v>0.02301571502481992</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2663492070059117</v>
+        <v>0.2682492070059118</v>
       </c>
       <c r="C92">
-        <v>-373.9227079053805</v>
+        <v>-380.6637505152781</v>
       </c>
       <c r="D92">
-        <v>129.7162920946195</v>
+        <v>128.6083494847219</v>
       </c>
       <c r="E92">
-        <v>505.2690000000001</v>
+        <v>510.9021000000001</v>
       </c>
       <c r="F92">
-        <v>506.979</v>
+        <v>512.6121000000001</v>
       </c>
       <c r="G92">
         <v>3.34</v>
@@ -8819,37 +8819,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M92">
-        <v>119.5456482</v>
+        <v>120.87393318</v>
       </c>
       <c r="N92">
-        <v>-116.7942196285714</v>
+        <v>-118.1225046085714</v>
       </c>
       <c r="O92">
-        <v>-29.19855490714286</v>
+        <v>-29.53062615214286</v>
       </c>
       <c r="P92">
-        <v>-87.59566472142858</v>
+        <v>-88.59187845642859</v>
       </c>
       <c r="Q92">
-        <v>-87.27566472142858</v>
+        <v>-88.2718784564286</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5535030576655358</v>
+        <v>0.6099145085172621</v>
       </c>
       <c r="T92">
-        <v>4.909876596134675</v>
+        <v>5.455418440149639</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.005753928756204969</v>
+        <v>0.005690698769873046</v>
       </c>
       <c r="W92">
-        <v>0.2344432235992869</v>
+        <v>0.234458133230064</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.02301571502481992</v>
+        <v>0.02276279507949219</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2682492070059118</v>
+        <v>0.2701492070059118</v>
       </c>
       <c r="C93">
-        <v>-380.6637505152781</v>
+        <v>-387.3860269259375</v>
       </c>
       <c r="D93">
-        <v>128.6083494847219</v>
+        <v>127.5191730740625</v>
       </c>
       <c r="E93">
-        <v>510.9021000000001</v>
+        <v>516.5352</v>
       </c>
       <c r="F93">
-        <v>512.6121000000001</v>
+        <v>518.2452000000001</v>
       </c>
       <c r="G93">
         <v>3.34</v>
@@ -8901,37 +8901,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M93">
-        <v>120.87393318</v>
+        <v>122.20221816</v>
       </c>
       <c r="N93">
-        <v>-118.1225046085714</v>
+        <v>-119.4507895885714</v>
       </c>
       <c r="O93">
-        <v>-29.53062615214286</v>
+        <v>-29.86269739714286</v>
       </c>
       <c r="P93">
-        <v>-88.59187845642859</v>
+        <v>-89.58809219142859</v>
       </c>
       <c r="Q93">
-        <v>-88.2718784564286</v>
+        <v>-89.26809219142859</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6099145085172621</v>
+        <v>0.6804288220819201</v>
       </c>
       <c r="T93">
-        <v>5.455418440149639</v>
+        <v>6.137345745168346</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.005690698769873046</v>
+        <v>0.005628843348461383</v>
       </c>
       <c r="W93">
-        <v>0.234458133230064</v>
+        <v>0.2344727187384328</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.02276279507949219</v>
+        <v>0.02251537339384557</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2701492070059118</v>
+        <v>0.2720492070059117</v>
       </c>
       <c r="C94">
-        <v>-387.3860269259375</v>
+        <v>-394.0900099228198</v>
       </c>
       <c r="D94">
-        <v>127.5191730740625</v>
+        <v>126.4482900771803</v>
       </c>
       <c r="E94">
-        <v>516.5352</v>
+        <v>522.1683</v>
       </c>
       <c r="F94">
-        <v>518.2452000000001</v>
+        <v>523.8783000000001</v>
       </c>
       <c r="G94">
         <v>3.34</v>
@@ -8983,37 +8983,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M94">
-        <v>122.20221816</v>
+        <v>123.53050314</v>
       </c>
       <c r="N94">
-        <v>-119.4507895885714</v>
+        <v>-120.7790745685714</v>
       </c>
       <c r="O94">
-        <v>-29.86269739714286</v>
+        <v>-30.19476864214286</v>
       </c>
       <c r="P94">
-        <v>-89.58809219142859</v>
+        <v>-90.58430592642858</v>
       </c>
       <c r="Q94">
-        <v>-89.26809219142859</v>
+        <v>-90.26430592642859</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6804288220819201</v>
+        <v>0.7710900823793373</v>
       </c>
       <c r="T94">
-        <v>6.137345745168346</v>
+        <v>7.014109423049539</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.005628843348461383</v>
+        <v>0.005568318151166099</v>
       </c>
       <c r="W94">
-        <v>0.2344727187384328</v>
+        <v>0.234486990579955</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.02251537339384557</v>
+        <v>0.02227327260466438</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2720492070059117</v>
+        <v>0.2739492070059118</v>
       </c>
       <c r="C95">
-        <v>-394.0900099228198</v>
+        <v>-400.7761565421772</v>
       </c>
       <c r="D95">
-        <v>126.4482900771803</v>
+        <v>125.3952434578229</v>
       </c>
       <c r="E95">
-        <v>522.1683</v>
+        <v>527.8014000000001</v>
       </c>
       <c r="F95">
-        <v>523.8783000000001</v>
+        <v>529.5114000000001</v>
       </c>
       <c r="G95">
         <v>3.34</v>
@@ -9065,37 +9065,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M95">
-        <v>123.53050314</v>
+        <v>124.85878812</v>
       </c>
       <c r="N95">
-        <v>-120.7790745685714</v>
+        <v>-122.1073595485715</v>
       </c>
       <c r="O95">
-        <v>-30.19476864214286</v>
+        <v>-30.52683988714286</v>
       </c>
       <c r="P95">
-        <v>-90.58430592642858</v>
+        <v>-91.58051966142858</v>
       </c>
       <c r="Q95">
-        <v>-90.26430592642859</v>
+        <v>-91.26051966142859</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7710900823793373</v>
+        <v>0.8919717627758939</v>
       </c>
       <c r="T95">
-        <v>7.014109423049539</v>
+        <v>8.183127660224466</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.005568318151166099</v>
+        <v>0.005509080724026033</v>
       </c>
       <c r="W95">
-        <v>0.234486990579955</v>
+        <v>0.2345009587652747</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.02227327260466438</v>
+        <v>0.02203632289610413</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2739492070059118</v>
+        <v>0.2758492070059118</v>
       </c>
       <c r="C96">
-        <v>-400.7761565421772</v>
+        <v>-407.4449087214248</v>
       </c>
       <c r="D96">
-        <v>125.3952434578229</v>
+        <v>124.3595912785753</v>
       </c>
       <c r="E96">
-        <v>527.8014000000001</v>
+        <v>533.4345000000001</v>
       </c>
       <c r="F96">
-        <v>529.5114000000001</v>
+        <v>535.1445000000001</v>
       </c>
       <c r="G96">
         <v>3.34</v>
@@ -9147,37 +9147,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M96">
-        <v>124.85878812</v>
+        <v>126.1870731</v>
       </c>
       <c r="N96">
-        <v>-122.1073595485715</v>
+        <v>-123.4356445285715</v>
       </c>
       <c r="O96">
-        <v>-30.52683988714286</v>
+        <v>-30.85891113214286</v>
       </c>
       <c r="P96">
-        <v>-91.58051966142858</v>
+        <v>-92.57673339642859</v>
       </c>
       <c r="Q96">
-        <v>-91.26051966142859</v>
+        <v>-92.2567333964286</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8919717627758939</v>
+        <v>1.061206115331073</v>
       </c>
       <c r="T96">
-        <v>8.183127660224466</v>
+        <v>9.819753192269362</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.005509080724026033</v>
+        <v>0.005451090400615232</v>
       </c>
       <c r="W96">
-        <v>0.2345009587652747</v>
+        <v>0.2345146328835349</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.02203632289610413</v>
+        <v>0.02180436160246102</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2758492070059118</v>
+        <v>0.2777492070059118</v>
       </c>
       <c r="C97">
-        <v>-407.4449087214248</v>
+        <v>-414.0966939175474</v>
       </c>
       <c r="D97">
-        <v>124.3595912785753</v>
+        <v>123.3409060824527</v>
       </c>
       <c r="E97">
-        <v>533.4345000000001</v>
+        <v>539.0676000000001</v>
       </c>
       <c r="F97">
-        <v>535.1445000000001</v>
+        <v>540.7776000000001</v>
       </c>
       <c r="G97">
         <v>3.34</v>
@@ -9229,37 +9229,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M97">
-        <v>126.1870731</v>
+        <v>127.51535808</v>
       </c>
       <c r="N97">
-        <v>-123.4356445285715</v>
+        <v>-124.7639295085715</v>
       </c>
       <c r="O97">
-        <v>-30.85891113214286</v>
+        <v>-31.19098237714286</v>
       </c>
       <c r="P97">
-        <v>-92.57673339642859</v>
+        <v>-93.57294713142859</v>
       </c>
       <c r="Q97">
-        <v>-92.2567333964286</v>
+        <v>-93.2529471314286</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.061206115331073</v>
+        <v>1.315057644163842</v>
       </c>
       <c r="T97">
-        <v>9.819753192269362</v>
+        <v>12.27469149033671</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.005451090400615232</v>
+        <v>0.005394308208942157</v>
       </c>
       <c r="W97">
-        <v>0.2345146328835349</v>
+        <v>0.2345280221243314</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.02180436160246102</v>
+        <v>0.02157723283576862</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2777492070059118</v>
+        <v>0.2796492070059118</v>
       </c>
       <c r="C98">
-        <v>-414.0966939175473</v>
+        <v>-420.7319256953589</v>
       </c>
       <c r="D98">
-        <v>123.3409060824527</v>
+        <v>122.3387743046411</v>
       </c>
       <c r="E98">
-        <v>539.0676</v>
+        <v>544.7007</v>
       </c>
       <c r="F98">
-        <v>540.7776</v>
+        <v>546.4107</v>
       </c>
       <c r="G98">
         <v>3.34</v>
@@ -9311,37 +9311,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M98">
-        <v>127.51535808</v>
+        <v>128.84364306</v>
       </c>
       <c r="N98">
-        <v>-124.7639295085714</v>
+        <v>-126.0922144885714</v>
       </c>
       <c r="O98">
-        <v>-31.19098237714286</v>
+        <v>-31.52305362214286</v>
       </c>
       <c r="P98">
-        <v>-93.57294713142858</v>
+        <v>-94.56916086642858</v>
       </c>
       <c r="Q98">
-        <v>-93.25294713142858</v>
+        <v>-94.24916086642858</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.315057644163838</v>
+        <v>1.738143525551785</v>
       </c>
       <c r="T98">
-        <v>12.27469149033668</v>
+        <v>16.3662553204489</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.005394308208942158</v>
+        <v>0.005338696784107704</v>
       </c>
       <c r="W98">
-        <v>0.2345280221243314</v>
+        <v>0.2345411352983074</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.02157723283576862</v>
+        <v>0.0213547871364308</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2796492070059118</v>
+        <v>0.2815492070059118</v>
       </c>
       <c r="C99">
-        <v>-420.7319256953589</v>
+        <v>-427.3510042873165</v>
       </c>
       <c r="D99">
-        <v>122.3387743046411</v>
+        <v>121.3527957126835</v>
       </c>
       <c r="E99">
-        <v>544.7007</v>
+        <v>550.3338</v>
       </c>
       <c r="F99">
-        <v>546.4107</v>
+        <v>552.0438</v>
       </c>
       <c r="G99">
         <v>3.34</v>
@@ -9393,37 +9393,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M99">
-        <v>128.84364306</v>
+        <v>130.17192804</v>
       </c>
       <c r="N99">
-        <v>-126.0922144885714</v>
+        <v>-127.4204994685714</v>
       </c>
       <c r="O99">
-        <v>-31.52305362214286</v>
+        <v>-31.85512486714286</v>
       </c>
       <c r="P99">
-        <v>-94.56916086642858</v>
+        <v>-95.56537460142857</v>
       </c>
       <c r="Q99">
-        <v>-94.24916086642858</v>
+        <v>-95.24537460142858</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.738143525551785</v>
+        <v>2.584315288327677</v>
       </c>
       <c r="T99">
-        <v>16.3662553204489</v>
+        <v>24.54938298067335</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.005338696784107704</v>
+        <v>0.005284220286310685</v>
       </c>
       <c r="W99">
-        <v>0.2345411352983074</v>
+        <v>0.234553980856488</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0213547871364308</v>
+        <v>0.02113688114524281</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2815492070059118</v>
+        <v>0.2834492070059118</v>
       </c>
       <c r="C100">
-        <v>-427.3510042873165</v>
+        <v>-433.9543171264798</v>
       </c>
       <c r="D100">
-        <v>121.3527957126835</v>
+        <v>120.3825828735203</v>
       </c>
       <c r="E100">
-        <v>550.3338</v>
+        <v>555.9669</v>
       </c>
       <c r="F100">
-        <v>552.0438</v>
+        <v>557.6769</v>
       </c>
       <c r="G100">
         <v>3.34</v>
@@ -9475,37 +9475,37 @@
         <v>2.751428571428571</v>
       </c>
       <c r="M100">
-        <v>130.17192804</v>
+        <v>131.50021302</v>
       </c>
       <c r="N100">
-        <v>-127.4204994685714</v>
+        <v>-128.7487844485715</v>
       </c>
       <c r="O100">
-        <v>-31.85512486714286</v>
+        <v>-32.18719611214286</v>
       </c>
       <c r="P100">
-        <v>-95.56537460142857</v>
+        <v>-96.5615883364286</v>
       </c>
       <c r="Q100">
-        <v>-95.24537460142858</v>
+        <v>-96.24158833642861</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.584315288327677</v>
+        <v>5.122830576655353</v>
       </c>
       <c r="T100">
-        <v>24.54938298067335</v>
+        <v>49.0987659613467</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.005284220286310685</v>
+        <v>0.005230844323822699</v>
       </c>
       <c r="W100">
-        <v>0.234553980856488</v>
+        <v>0.2345665669084426</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.02113688114524281</v>
+        <v>0.0209233772952907</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2834492070059118</v>
-      </c>
-      <c r="C101">
-        <v>-433.9543171264798</v>
-      </c>
-      <c r="D101">
-        <v>120.3825828735203</v>
-      </c>
-      <c r="E101">
-        <v>555.9669</v>
-      </c>
-      <c r="F101">
-        <v>557.6769</v>
-      </c>
-      <c r="G101">
-        <v>3.34</v>
-      </c>
-      <c r="H101">
-        <v>561.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.071428571428571</v>
-      </c>
-      <c r="K101">
-        <v>0.3199999999999998</v>
-      </c>
-      <c r="L101">
-        <v>2.751428571428571</v>
-      </c>
-      <c r="M101">
-        <v>131.50021302</v>
-      </c>
-      <c r="N101">
-        <v>-128.7487844485715</v>
-      </c>
-      <c r="O101">
-        <v>-32.18719611214286</v>
-      </c>
-      <c r="P101">
-        <v>-96.5615883364286</v>
-      </c>
-      <c r="Q101">
-        <v>-96.24158833642861</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.122830576655353</v>
-      </c>
-      <c r="T101">
-        <v>49.0987659613467</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.005230844323822699</v>
-      </c>
-      <c r="W101">
-        <v>0.2345665669084426</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0209233772952907</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
